--- a/excel_project/Employee Attendance Data Analysis.xlsx
+++ b/excel_project/Employee Attendance Data Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cabdi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raadsan Teach\Desktop\𝗗𝗮𝘁𝗮 𝗦𝗰𝗶𝗲𝗻𝗰𝗲 &amp; 𝗠𝗮𝗰𝗵𝗶𝗻𝗲 𝗟𝗲𝗮𝗿𝗻𝗶𝗻𝗴\excel_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F951743-DC0C-4D55-B4B4-EF439DF713C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F94A2101-F726-4F57-986D-72AD153440DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{9D7EAFDF-D859-4F86-87FA-928A73C89F4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{9D7EAFDF-D859-4F86-87FA-928A73C89F4C}"/>
   </bookViews>
   <sheets>
     <sheet name="row-data" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3366" uniqueCount="277">
   <si>
     <t>Employee_ID</t>
   </si>
@@ -1316,28 +1316,6 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1353,52 +1331,40 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="hh:mm"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="hh:mm"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="25" formatCode="h:mm"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="hh:mm"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     </dxf>
@@ -1425,6 +1391,40 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="25" formatCode="h:mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1453,7 +1453,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Abdinajib123.xlsx]PivotTables!PivotTable1</c:name>
+    <c:name>[Employee Attendance Data Analysis.xlsx]PivotTables!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1834,28 +1834,475 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PivotTables!$A$5:$A$7</c:f>
+              <c:f>PivotTables!$A$5:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Finance</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PivotTables!$B$5:$B$7</c:f>
+              <c:f>PivotTables!$B$5:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8FBA-4F9C-B488-0161CA6BFB6E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Late</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
                 <c:pt idx="1">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$C$5:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-981A-4353-8E0C-D814DB20945C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Present</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$D$5:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-981A-4353-8E0C-D814DB20945C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Remote</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$E$5:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -1863,7 +2310,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8FBA-4F9C-B488-0161CA6BFB6E}"/>
+              <c16:uniqueId val="{00000002-981A-4353-8E0C-D814DB20945C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2161,7 +2608,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Abdinajib123.xlsx]PivotTables!PivotTable2</c:name>
+    <c:name>[Employee Attendance Data Analysis.xlsx]PivotTables!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2378,7 +2825,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg2"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -2397,7 +2844,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -2414,6 +2861,15 @@
             <c:idx val="3"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000002-F79A-4C11-A2A5-6A008DF5317B}"/>
@@ -2424,6 +2880,17 @@
             <c:idx val="4"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-F79A-4C11-A2A5-6A008DF5317B}"/>
@@ -2434,6 +2901,15 @@
             <c:idx val="5"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000006-F79A-4C11-A2A5-6A008DF5317B}"/>
@@ -2442,29 +2918,53 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>PivotTables!$A$20:$A$22</c:f>
+              <c:f>PivotTables!$A$20:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Finance</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PivotTables!$B$20:$B$22</c:f>
+              <c:f>PivotTables!$B$20:$B$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2747,7 +3247,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Abdinajib123.xlsx]PivotTables!PivotTable3</c:name>
+    <c:name>[Employee Attendance Data Analysis.xlsx]PivotTables!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3049,7 +3549,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PivotTables!$B$35:$B$36</c:f>
+              <c:f>PivotTables!$B$39:$B$40</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3128,23 +3628,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PivotTables!$A$37:$A$38</c:f>
+              <c:f>PivotTables!$A$41:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Evening</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Morning</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PivotTables!$B$37:$B$38</c:f>
+              <c:f>PivotTables!$B$41:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3152,6 +3658,357 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-40A2-418F-888E-EEE239283106}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$C$39:$C$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Late</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$41:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Evening</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Morning</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$C$41:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1BB6-4C02-93AF-001C89273A1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$D$39:$D$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Present</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$41:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Evening</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Morning</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$D$41:$D$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1BB6-4C02-93AF-001C89273A1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$E$39:$E$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Remote</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$41:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Evening</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Morning</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$E$41:$E$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1BB6-4C02-93AF-001C89273A1F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3389,7 +4246,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Abdinajib123.xlsx]PivotTables!PivotTable4</c:name>
+    <c:name>[Employee Attendance Data Analysis.xlsx]PivotTables!PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3556,7 +4413,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PivotTables!$B$54</c:f>
+              <c:f>PivotTables!$B$60</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3711,7 +4568,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PivotTables!$A$55:$A$59</c:f>
+              <c:f>PivotTables!$A$61:$A$65</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -3731,21 +4588,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PivotTables!$B$55:$B$59</c:f>
+              <c:f>PivotTables!$B$61:$B$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>17</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>116</c:v>
+                  <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3990,7 +4847,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Abdinajib123.xlsx]PivotTables!PivotTable1</c:name>
+    <c:name>[Employee Attendance Data Analysis.xlsx]PivotTables!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -4837,28 +5694,475 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PivotTables!$A$5:$A$7</c:f>
+              <c:f>PivotTables!$A$5:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Finance</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PivotTables!$B$5:$B$7</c:f>
+              <c:f>PivotTables!$B$5:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-761A-40C0-A255-E4F0F78624AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Late</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
                 <c:pt idx="1">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$C$5:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5907-470D-B64D-F340798E8DC6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Present</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$D$5:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5907-470D-B64D-F340798E8DC6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Remote</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$E$5:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -4866,7 +6170,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-761A-40C0-A255-E4F0F78624AB}"/>
+              <c16:uniqueId val="{00000002-5907-470D-B64D-F340798E8DC6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5164,7 +6468,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Abdinajib123.xlsx]PivotTables!PivotTable2</c:name>
+    <c:name>[Employee Attendance Data Analysis.xlsx]PivotTables!PivotTable2</c:name>
     <c:fmtId val="5"/>
   </c:pivotSource>
   <c:chart>
@@ -5617,7 +6921,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg2"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -5636,7 +6940,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -5653,6 +6957,15 @@
             <c:idx val="3"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-CFAF-46D1-965C-E14A57923736}"/>
@@ -5663,6 +6976,17 @@
             <c:idx val="4"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000007-CFAF-46D1-965C-E14A57923736}"/>
@@ -5673,6 +6997,15 @@
             <c:idx val="5"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000009-CFAF-46D1-965C-E14A57923736}"/>
@@ -5681,29 +7014,53 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>PivotTables!$A$20:$A$22</c:f>
+              <c:f>PivotTables!$A$20:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Administration</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Finance</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PivotTables!$B$20:$B$22</c:f>
+              <c:f>PivotTables!$B$20:$B$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5986,7 +7343,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Abdinajib123.xlsx]PivotTables!PivotTable3</c:name>
+    <c:name>[Employee Attendance Data Analysis.xlsx]PivotTables!PivotTable3</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -6712,7 +8069,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PivotTables!$B$35:$B$36</c:f>
+              <c:f>PivotTables!$B$39:$B$40</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6791,23 +8148,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PivotTables!$A$37:$A$38</c:f>
+              <c:f>PivotTables!$A$41:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Evening</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Morning</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PivotTables!$B$37:$B$38</c:f>
+              <c:f>PivotTables!$B$41:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6815,6 +8178,357 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-71AF-49A2-BB07-B288FA423651}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$C$39:$C$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Late</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$41:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Evening</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Morning</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$C$41:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D401-425E-8E99-D41981BC0373}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$D$39:$D$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Present</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$41:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Evening</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Morning</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$D$41:$D$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D401-425E-8E99-D41981BC0373}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$E$39:$E$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Remote</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$41:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Evening</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Morning</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$E$41:$E$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D401-425E-8E99-D41981BC0373}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7052,7 +8766,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Abdinajib123.xlsx]PivotTables!PivotTable4</c:name>
+    <c:name>[Employee Attendance Data Analysis.xlsx]PivotTables!PivotTable4</c:name>
     <c:fmtId val="5"/>
   </c:pivotSource>
   <c:chart>
@@ -7426,7 +9140,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>PivotTables!$B$54</c:f>
+              <c:f>PivotTables!$B$60</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7523,7 +9237,7 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>PivotTables!$A$55:$A$59</c:f>
+              <c:f>PivotTables!$A$61:$A$65</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -7543,21 +9257,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PivotTables!$B$55:$B$59</c:f>
+              <c:f>PivotTables!$B$61:$B$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>17</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>116</c:v>
+                  <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12140,15 +13854,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12175,16 +13889,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
+      <xdr:colOff>371475</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12211,16 +13925,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>61912</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>604837</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>366712</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
+      <xdr:colOff>376237</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12247,16 +13961,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>119062</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>595312</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>423862</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:colOff>366712</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15635,18 +17349,18 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B7770CC-9600-491A-A8A4-A73C2D0163DE}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A54:B59" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B7770CC-9600-491A-A8A4-A73C2D0163DE}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="A60:B65" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="4"/>
         <item x="1"/>
         <item x="2"/>
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item x="5"/>
         <item t="default"/>
       </items>
@@ -15691,7 +17405,7 @@
   <dataFields count="1">
     <dataField name="Count of Employee_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="10">
+  <chartFormats count="20">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -15806,6 +17520,120 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="18" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -15820,8 +17648,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04E98BA2-B21B-41A9-8D6B-B61CD1B21809}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A35:C38" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04E98BA2-B21B-41A9-8D6B-B61CD1B21809}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="A39:F43" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="164" showAll="0">
@@ -16043,11 +17871,11 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="4"/>
         <item x="1"/>
         <item x="2"/>
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item x="5"/>
         <item t="default"/>
       </items>
@@ -16058,16 +17886,16 @@
     <pivotField axis="axisCol" showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16075,9 +17903,12 @@
   <rowFields count="1">
     <field x="7"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="3">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -16086,9 +17917,18 @@
   <colFields count="1">
     <field x="6"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="5">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -16208,18 +18048,18 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6F1B1452-885A-4950-8B4D-09D91CFCE677}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A19:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6F1B1452-885A-4950-8B4D-09D91CFCE677}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+  <location ref="A19:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="4"/>
         <item x="1"/>
         <item x="2"/>
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item x="5"/>
         <item t="default"/>
       </items>
@@ -16230,16 +18070,16 @@
     <pivotField showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
       <items count="3">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16247,12 +18087,24 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
     <i>
       <x v="1"/>
     </i>
     <i>
+      <x v="2"/>
+    </i>
+    <i>
       <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -16417,8 +18269,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FC26722-1116-4454-BEBF-77D55F56557F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:C7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FC26722-1116-4454-BEBF-77D55F56557F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+  <location ref="A3:F11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="164" showAll="0">
@@ -16640,11 +18492,11 @@
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="4"/>
         <item x="1"/>
         <item x="2"/>
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item x="5"/>
         <item t="default"/>
       </items>
@@ -16655,16 +18507,16 @@
     <pivotField axis="axisCol" showAll="0">
       <items count="5">
         <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
       <items count="3">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16672,12 +18524,24 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
     <i>
       <x v="1"/>
     </i>
     <i>
+      <x v="2"/>
+    </i>
+    <i>
       <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -16686,9 +18550,18 @@
   <colFields count="1">
     <field x="6"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="5">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -16818,11 +18691,11 @@
   <data>
     <tabular pivotCacheId="968610972">
       <items count="6">
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="4" s="1"/>
         <i x="1" s="1"/>
         <i x="2" s="1"/>
-        <i x="3"/>
+        <i x="3" s="1"/>
         <i x="5" s="1"/>
       </items>
     </tabular>
@@ -16841,7 +18714,7 @@
     <tabular pivotCacheId="968610972">
       <items count="2">
         <i x="0" s="1"/>
-        <i x="1"/>
+        <i x="1" s="1"/>
       </items>
     </tabular>
   </data>
@@ -16859,9 +18732,9 @@
     <tabular pivotCacheId="968610972">
       <items count="4">
         <i x="3" s="1"/>
-        <i x="1"/>
-        <i x="0"/>
-        <i x="2"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
       </items>
     </tabular>
   </data>
@@ -16877,11 +18750,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C55F5AC-C514-4928-874F-391BF50071E4}" name="Table1" displayName="Table1" ref="A1:G301" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C55F5AC-C514-4928-874F-391BF50071E4}" name="Table1" displayName="Table1" ref="A1:G301" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:G301" xr:uid="{8C55F5AC-C514-4928-874F-391BF50071E4}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{24489714-A500-4CBF-B6EF-8CFB55BF5640}" name="Employee_ID"/>
-    <tableColumn id="2" xr3:uid="{4D754965-B075-4351-A8C2-190B9121C928}" name="Attendance_Date" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4D754965-B075-4351-A8C2-190B9121C928}" name="Attendance_Date" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{1064BF96-8238-4ADC-B3C1-ACC0BFA13D86}" name="Department"/>
     <tableColumn id="4" xr3:uid="{E068EBA8-12DF-42F8-93D4-2EF19892C530}" name="Shift"/>
     <tableColumn id="5" xr3:uid="{C6155423-6F20-4446-9763-35462FE31B6F}" name="Check_In"/>
@@ -16897,11 +18770,11 @@
   <autoFilter ref="A1:H262" xr:uid="{1D9294AB-0645-4EEC-904E-A49D59462F17}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{7BB2194F-A94F-4720-AF88-80E5DF0603BC}" name="Employee_ID" dataCellStyle="Normal"/>
-    <tableColumn id="2" xr3:uid="{1EAD1C51-E168-4976-B173-48B8AC590807}" name="Attendance_Date" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{1EAD1C51-E168-4976-B173-48B8AC590807}" name="Attendance_Date" dataDxfId="6" dataCellStyle="Normal"/>
     <tableColumn id="3" xr3:uid="{3EBDBCF4-4741-4402-B568-7FF7F505A374}" name="Department" dataCellStyle="Normal"/>
     <tableColumn id="4" xr3:uid="{83284870-43E2-4A00-A7A1-011401C98054}" name="Shift" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{1A8D278C-45A4-43D5-B3F3-167E7601EED2}" name="Check_In" dataDxfId="2" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{0273EDA2-85FA-44B1-BE5E-6D8D830DB842}" name="Check_Out" dataDxfId="1" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{1A8D278C-45A4-43D5-B3F3-167E7601EED2}" name="Check_In" dataDxfId="5" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{0273EDA2-85FA-44B1-BE5E-6D8D830DB842}" name="Check_Out" dataDxfId="4" dataCellStyle="Normal"/>
     <tableColumn id="7" xr3:uid="{E72137E6-C5C9-4BBA-9E18-ED2C544E01DE}" name="Attendance_Status" dataCellStyle="Normal"/>
     <tableColumn id="8" xr3:uid="{7C3C5148-47C1-4AD1-A6BB-685EACE462B3}" name="Correct Shift" dataCellStyle="Normal">
       <calculatedColumnFormula>IFERROR(IF(TIMEVALUE(E2)&lt;TIME(12,0,0),"Morning","Evening"),D2)</calculatedColumnFormula>
@@ -16951,7 +18824,7 @@
   <autoFilter ref="S22:T24" xr:uid="{0A8DC1AB-55B9-4B8D-B7E2-A5CCD550DC8D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5B36A450-579B-4FB0-B26F-5116F33A8CD1}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{49E8A8EB-CF31-4166-8388-D476AC18F0C0}" name="Column2" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{49E8A8EB-CF31-4166-8388-D476AC18F0C0}" name="Column2" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16962,7 +18835,7 @@
   <autoFilter ref="S35:T36" xr:uid="{AA0C5FD1-D4EB-4950-A60A-3F75286241F3}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{30351217-FA0B-4383-8DDC-E43A2F956C34}" name="Morning Check_Out Median"/>
-    <tableColumn id="2" xr3:uid="{C9C1C5D0-EAD3-4E1C-85D9-45FDF3DE1D87}" name="17:07" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{C9C1C5D0-EAD3-4E1C-85D9-45FDF3DE1D87}" name="17:07" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17283,15 +19156,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CF856E-D65F-4F88-B27D-0D8340D8DD21}">
   <dimension ref="A1:G301"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -23922,24 +25795,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264A1061-A038-4AAD-B54C-D0C14EDAB05C}">
   <dimension ref="A1:AB262"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
     <col min="23" max="23" width="18" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="83.26953125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="83.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="18" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="65.26953125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="65.28515625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23947,7 +25820,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -23956,10 +25829,10 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -23973,7 +25846,7 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="33">
+      <c r="B2" s="23">
         <v>45939</v>
       </c>
       <c r="C2" t="s">
@@ -23982,10 +25855,10 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="s">
@@ -24000,7 +25873,7 @@
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="23">
         <v>46103</v>
       </c>
       <c r="C3" t="s">
@@ -24009,10 +25882,10 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
@@ -24027,7 +25900,7 @@
       <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="23">
         <v>45778</v>
       </c>
       <c r="C4" t="s">
@@ -24036,10 +25909,10 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G4" t="s">
@@ -24054,7 +25927,7 @@
       <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="23">
         <v>46026</v>
       </c>
       <c r="C5" t="s">
@@ -24063,10 +25936,10 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
@@ -24100,7 +25973,7 @@
       <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="23">
         <v>45932</v>
       </c>
       <c r="C6" t="s">
@@ -24109,10 +25982,10 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G6" t="s">
@@ -24145,7 +26018,7 @@
       <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="23">
         <v>45696</v>
       </c>
       <c r="C7" t="s">
@@ -24154,10 +26027,10 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="16" t="s">
         <v>32</v>
       </c>
       <c r="G7" t="s">
@@ -24190,7 +26063,7 @@
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="23">
         <v>45692</v>
       </c>
       <c r="C8" t="s">
@@ -24199,10 +26072,10 @@
       <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="16" t="s">
         <v>38</v>
       </c>
       <c r="G8" t="s">
@@ -24235,7 +26108,7 @@
       <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="23">
         <v>45748</v>
       </c>
       <c r="C9" t="s">
@@ -24244,10 +26117,10 @@
       <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G9" t="s">
@@ -24280,7 +26153,7 @@
       <c r="A10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="23">
         <v>46210</v>
       </c>
       <c r="C10" t="s">
@@ -24289,10 +26162,10 @@
       <c r="D10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="16" t="s">
         <v>44</v>
       </c>
       <c r="G10" t="s">
@@ -24325,7 +26198,7 @@
       <c r="A11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="23">
         <v>45921</v>
       </c>
       <c r="C11" t="s">
@@ -24334,7 +26207,7 @@
       <c r="D11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G11" t="s">
@@ -24361,7 +26234,7 @@
       <c r="A12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="23">
         <v>45774</v>
       </c>
       <c r="C12" t="s">
@@ -24370,10 +26243,10 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G12" t="s">
@@ -24406,7 +26279,7 @@
       <c r="A13" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="23">
         <v>46168</v>
       </c>
       <c r="C13" t="s">
@@ -24415,10 +26288,10 @@
       <c r="D13" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G13" t="s">
@@ -24440,7 +26313,7 @@
       <c r="A14" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="23">
         <v>45671</v>
       </c>
       <c r="C14" t="s">
@@ -24449,10 +26322,10 @@
       <c r="D14" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G14" t="s">
@@ -24474,7 +26347,7 @@
       <c r="A15" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="23">
         <v>46167</v>
       </c>
       <c r="C15" t="s">
@@ -24483,10 +26356,10 @@
       <c r="D15" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="16" t="s">
         <v>55</v>
       </c>
       <c r="G15" t="s">
@@ -24508,7 +26381,7 @@
       <c r="A16" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="23">
         <v>45986</v>
       </c>
       <c r="C16" t="s">
@@ -24517,10 +26390,10 @@
       <c r="D16" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G16" t="s">
@@ -24542,7 +26415,7 @@
       <c r="A17" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="23">
         <v>45783</v>
       </c>
       <c r="C17" t="s">
@@ -24551,10 +26424,10 @@
       <c r="D17" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G17" t="s">
@@ -24576,7 +26449,7 @@
       <c r="A18" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="23">
         <v>45933</v>
       </c>
       <c r="C18" t="s">
@@ -24585,10 +26458,10 @@
       <c r="D18" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="16" t="s">
         <v>61</v>
       </c>
       <c r="G18" t="s">
@@ -24610,7 +26483,7 @@
       <c r="A19" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="23">
         <v>46125</v>
       </c>
       <c r="C19" t="s">
@@ -24619,10 +26492,10 @@
       <c r="D19" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="16" t="s">
         <v>64</v>
       </c>
       <c r="G19" t="s">
@@ -24637,7 +26510,7 @@
       <c r="A20" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="23">
         <v>46095</v>
       </c>
       <c r="C20" t="s">
@@ -24646,10 +26519,10 @@
       <c r="D20" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="16" t="s">
         <v>67</v>
       </c>
       <c r="G20" t="s">
@@ -24664,7 +26537,7 @@
       <c r="A21" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="23">
         <v>45787</v>
       </c>
       <c r="C21" t="s">
@@ -24673,10 +26546,10 @@
       <c r="D21" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="16" t="s">
         <v>69</v>
       </c>
       <c r="G21" t="s">
@@ -24691,7 +26564,7 @@
       <c r="A22" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="23">
         <v>46012</v>
       </c>
       <c r="C22" t="s">
@@ -24700,10 +26573,10 @@
       <c r="D22" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="16" t="s">
         <v>61</v>
       </c>
       <c r="G22" t="s">
@@ -24724,7 +26597,7 @@
       <c r="A23" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="23">
         <v>45927</v>
       </c>
       <c r="C23" t="s">
@@ -24733,10 +26606,10 @@
       <c r="D23" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="16" t="s">
         <v>72</v>
       </c>
       <c r="G23" t="s">
@@ -24757,7 +26630,7 @@
       <c r="A24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="23">
         <v>45924</v>
       </c>
       <c r="C24" t="s">
@@ -24766,10 +26639,10 @@
       <c r="D24" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G24" t="s">
@@ -24790,7 +26663,7 @@
       <c r="A25" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="23">
         <v>46136</v>
       </c>
       <c r="C25" t="s">
@@ -24799,10 +26672,10 @@
       <c r="D25" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G25" t="s">
@@ -24817,7 +26690,7 @@
       <c r="A26" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="33">
+      <c r="B26" s="23">
         <v>45697</v>
       </c>
       <c r="C26" t="s">
@@ -24826,10 +26699,10 @@
       <c r="D26" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="16" t="s">
         <v>32</v>
       </c>
       <c r="G26" t="s">
@@ -24844,7 +26717,7 @@
       <c r="A27" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="23">
         <v>46014</v>
       </c>
       <c r="C27" t="s">
@@ -24853,10 +26726,10 @@
       <c r="D27" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="16">
         <v>0.58680555555555558</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G27" t="s">
@@ -24871,7 +26744,7 @@
       <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="33">
+      <c r="B28" s="23">
         <v>46228</v>
       </c>
       <c r="C28" t="s">
@@ -24880,10 +26753,10 @@
       <c r="D28" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G28" t="s">
@@ -24899,7 +26772,7 @@
       <c r="A29" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="23">
         <v>45955</v>
       </c>
       <c r="C29" t="s">
@@ -24908,10 +26781,10 @@
       <c r="D29" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="16" t="s">
         <v>69</v>
       </c>
       <c r="G29" t="s">
@@ -24927,7 +26800,7 @@
       <c r="A30" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="23">
         <v>46130</v>
       </c>
       <c r="C30" t="s">
@@ -24936,10 +26809,10 @@
       <c r="D30" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G30" t="s">
@@ -24954,7 +26827,7 @@
       <c r="A31" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="23">
         <v>46111</v>
       </c>
       <c r="C31" t="s">
@@ -24963,10 +26836,10 @@
       <c r="D31" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="F31" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G31" t="s">
@@ -24981,7 +26854,7 @@
       <c r="A32" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="23">
         <v>46167</v>
       </c>
       <c r="C32" t="s">
@@ -24990,10 +26863,10 @@
       <c r="D32" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="16" t="s">
         <v>86</v>
       </c>
       <c r="G32" t="s">
@@ -25008,7 +26881,7 @@
       <c r="A33" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="23">
         <v>45939</v>
       </c>
       <c r="C33" t="s">
@@ -25017,10 +26890,10 @@
       <c r="D33" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="16" t="s">
         <v>88</v>
       </c>
       <c r="G33" t="s">
@@ -25035,7 +26908,7 @@
       <c r="A34" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="23">
         <v>45869</v>
       </c>
       <c r="C34" t="s">
@@ -25044,10 +26917,10 @@
       <c r="D34" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="16" t="s">
         <v>91</v>
       </c>
       <c r="G34" t="s">
@@ -25062,7 +26935,7 @@
       <c r="A35" t="s">
         <v>92</v>
       </c>
-      <c r="B35" s="33">
+      <c r="B35" s="23">
         <v>46026</v>
       </c>
       <c r="C35" t="s">
@@ -25071,10 +26944,10 @@
       <c r="D35" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="16" t="s">
         <v>44</v>
       </c>
       <c r="G35" t="s">
@@ -25095,7 +26968,7 @@
       <c r="A36" t="s">
         <v>93</v>
       </c>
-      <c r="B36" s="33">
+      <c r="B36" s="23">
         <v>45918</v>
       </c>
       <c r="C36" t="s">
@@ -25104,10 +26977,10 @@
       <c r="D36" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="16" t="s">
         <v>94</v>
       </c>
       <c r="G36" t="s">
@@ -25128,7 +27001,7 @@
       <c r="A37" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="33">
+      <c r="B37" s="23">
         <v>45876</v>
       </c>
       <c r="C37" t="s">
@@ -25137,10 +27010,10 @@
       <c r="D37" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="16" t="s">
         <v>98</v>
       </c>
       <c r="G37" t="s">
@@ -25155,7 +27028,7 @@
       <c r="A38" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="33">
+      <c r="B38" s="23">
         <v>45762</v>
       </c>
       <c r="C38" t="s">
@@ -25164,10 +27037,10 @@
       <c r="D38" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="16" t="s">
         <v>100</v>
       </c>
       <c r="G38" t="s">
@@ -25182,7 +27055,7 @@
       <c r="A39" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="33">
+      <c r="B39" s="23">
         <v>46184</v>
       </c>
       <c r="C39" t="s">
@@ -25191,10 +27064,10 @@
       <c r="D39" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="16" t="s">
         <v>102</v>
       </c>
       <c r="G39" t="s">
@@ -25209,7 +27082,7 @@
       <c r="A40" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="33">
+      <c r="B40" s="23">
         <v>45900</v>
       </c>
       <c r="C40" t="s">
@@ -25218,10 +27091,10 @@
       <c r="D40" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="16" t="s">
         <v>104</v>
       </c>
       <c r="G40" t="s">
@@ -25236,7 +27109,7 @@
       <c r="A41" t="s">
         <v>105</v>
       </c>
-      <c r="B41" s="33">
+      <c r="B41" s="23">
         <v>46122</v>
       </c>
       <c r="C41" t="s">
@@ -25245,10 +27118,10 @@
       <c r="D41" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="24" t="s">
+      <c r="E41" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F41" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G41" t="s">
@@ -25263,7 +27136,7 @@
       <c r="A42" t="s">
         <v>106</v>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="23">
         <v>45898</v>
       </c>
       <c r="C42" t="s">
@@ -25272,10 +27145,10 @@
       <c r="D42" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F42" s="16" t="s">
         <v>107</v>
       </c>
       <c r="G42" t="s">
@@ -25290,7 +27163,7 @@
       <c r="A43" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="33">
+      <c r="B43" s="23">
         <v>45706</v>
       </c>
       <c r="C43" t="s">
@@ -25299,10 +27172,10 @@
       <c r="D43" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="E43" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F43" s="24" t="s">
+      <c r="F43" s="16" t="s">
         <v>108</v>
       </c>
       <c r="G43" t="s">
@@ -25317,7 +27190,7 @@
       <c r="A44" t="s">
         <v>109</v>
       </c>
-      <c r="B44" s="33">
+      <c r="B44" s="23">
         <v>45751</v>
       </c>
       <c r="C44" t="s">
@@ -25326,10 +27199,10 @@
       <c r="D44" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="24" t="s">
+      <c r="E44" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="24" t="s">
+      <c r="F44" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G44" t="s">
@@ -25344,7 +27217,7 @@
       <c r="A45" t="s">
         <v>110</v>
       </c>
-      <c r="B45" s="33">
+      <c r="B45" s="23">
         <v>45748</v>
       </c>
       <c r="C45" t="s">
@@ -25353,10 +27226,10 @@
       <c r="D45" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G45" t="s">
@@ -25371,7 +27244,7 @@
       <c r="A46" t="s">
         <v>112</v>
       </c>
-      <c r="B46" s="33">
+      <c r="B46" s="23">
         <v>46185</v>
       </c>
       <c r="C46" t="s">
@@ -25380,10 +27253,10 @@
       <c r="D46" t="s">
         <v>18</v>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="16">
         <v>0.58680555555555558</v>
       </c>
-      <c r="F46" s="24" t="s">
+      <c r="F46" s="16" t="s">
         <v>55</v>
       </c>
       <c r="G46" t="s">
@@ -25402,7 +27275,7 @@
       <c r="A47" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="33">
+      <c r="B47" s="23">
         <v>45874</v>
       </c>
       <c r="C47" t="s">
@@ -25411,10 +27284,10 @@
       <c r="D47" t="s">
         <v>18</v>
       </c>
-      <c r="E47" s="24" t="s">
+      <c r="E47" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="24" t="s">
+      <c r="F47" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G47" t="s">
@@ -25429,7 +27302,7 @@
       <c r="A48" t="s">
         <v>113</v>
       </c>
-      <c r="B48" s="33">
+      <c r="B48" s="23">
         <v>45870</v>
       </c>
       <c r="C48" t="s">
@@ -25438,10 +27311,10 @@
       <c r="D48" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="24" t="s">
+      <c r="E48" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="16">
         <v>0.9291666666666667</v>
       </c>
       <c r="G48" t="s">
@@ -25456,7 +27329,7 @@
       <c r="A49" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="33">
+      <c r="B49" s="23">
         <v>46009</v>
       </c>
       <c r="C49" t="s">
@@ -25465,10 +27338,10 @@
       <c r="D49" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="24" t="s">
+      <c r="E49" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F49" s="24" t="s">
+      <c r="F49" s="16" t="s">
         <v>115</v>
       </c>
       <c r="G49" t="s">
@@ -25483,7 +27356,7 @@
       <c r="A50" t="s">
         <v>76</v>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="23">
         <v>45804</v>
       </c>
       <c r="C50" t="s">
@@ -25492,10 +27365,10 @@
       <c r="D50" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="E50" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F50" s="24" t="s">
+      <c r="F50" s="16" t="s">
         <v>116</v>
       </c>
       <c r="G50" t="s">
@@ -25510,7 +27383,7 @@
       <c r="A51" t="s">
         <v>118</v>
       </c>
-      <c r="B51" s="33">
+      <c r="B51" s="23">
         <v>46206</v>
       </c>
       <c r="C51" t="s">
@@ -25519,10 +27392,10 @@
       <c r="D51" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F51" s="24" t="s">
+      <c r="F51" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G51" t="s">
@@ -25537,7 +27410,7 @@
       <c r="A52" t="s">
         <v>119</v>
       </c>
-      <c r="B52" s="33">
+      <c r="B52" s="23">
         <v>46229</v>
       </c>
       <c r="C52" t="s">
@@ -25546,10 +27419,10 @@
       <c r="D52" t="s">
         <v>18</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E52" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F52" s="24" t="s">
+      <c r="F52" s="16" t="s">
         <v>86</v>
       </c>
       <c r="G52" t="s">
@@ -25564,7 +27437,7 @@
       <c r="A53" t="s">
         <v>45</v>
       </c>
-      <c r="B53" s="33">
+      <c r="B53" s="23">
         <v>46214</v>
       </c>
       <c r="C53" t="s">
@@ -25573,10 +27446,10 @@
       <c r="D53" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F53" s="24" t="s">
+      <c r="F53" s="16" t="s">
         <v>120</v>
       </c>
       <c r="G53" t="s">
@@ -25591,7 +27464,7 @@
       <c r="A54" t="s">
         <v>89</v>
       </c>
-      <c r="B54" s="33">
+      <c r="B54" s="23">
         <v>45673</v>
       </c>
       <c r="C54" t="s">
@@ -25600,10 +27473,10 @@
       <c r="D54" t="s">
         <v>18</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="E54" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F54" s="24" t="s">
+      <c r="F54" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G54" t="s">
@@ -25618,7 +27491,7 @@
       <c r="A55" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="33">
+      <c r="B55" s="23">
         <v>46232</v>
       </c>
       <c r="C55" t="s">
@@ -25627,10 +27500,10 @@
       <c r="D55" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F55" s="24" t="s">
+      <c r="F55" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G55" t="s">
@@ -25645,7 +27518,7 @@
       <c r="A56" t="s">
         <v>103</v>
       </c>
-      <c r="B56" s="33">
+      <c r="B56" s="23">
         <v>46026</v>
       </c>
       <c r="C56" t="s">
@@ -25654,10 +27527,10 @@
       <c r="D56" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F56" s="24" t="s">
+      <c r="F56" s="16" t="s">
         <v>120</v>
       </c>
       <c r="G56" t="s">
@@ -25672,7 +27545,7 @@
       <c r="A57" t="s">
         <v>121</v>
       </c>
-      <c r="B57" s="33">
+      <c r="B57" s="23">
         <v>46022</v>
       </c>
       <c r="C57" t="s">
@@ -25681,10 +27554,10 @@
       <c r="D57" t="s">
         <v>18</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F57" s="24" t="s">
+      <c r="F57" s="16" t="s">
         <v>115</v>
       </c>
       <c r="G57" t="s">
@@ -25699,7 +27572,7 @@
       <c r="A58" t="s">
         <v>79</v>
       </c>
-      <c r="B58" s="33">
+      <c r="B58" s="23">
         <v>45722</v>
       </c>
       <c r="C58" t="s">
@@ -25708,10 +27581,10 @@
       <c r="D58" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E58" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F58" s="24" t="s">
+      <c r="F58" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G58" t="s">
@@ -25726,7 +27599,7 @@
       <c r="A59" t="s">
         <v>46</v>
       </c>
-      <c r="B59" s="33">
+      <c r="B59" s="23">
         <v>45953</v>
       </c>
       <c r="C59" t="s">
@@ -25735,10 +27608,10 @@
       <c r="D59" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="24" t="s">
+      <c r="E59" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F59" s="24" t="s">
+      <c r="F59" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G59" t="s">
@@ -25753,7 +27626,7 @@
       <c r="A60" t="s">
         <v>113</v>
       </c>
-      <c r="B60" s="33">
+      <c r="B60" s="23">
         <v>46095</v>
       </c>
       <c r="C60" t="s">
@@ -25762,10 +27635,10 @@
       <c r="D60" t="s">
         <v>18</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="E60" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="F60" s="24" t="s">
+      <c r="F60" s="16" t="s">
         <v>126</v>
       </c>
       <c r="G60" t="s">
@@ -25780,7 +27653,7 @@
       <c r="A61" t="s">
         <v>127</v>
       </c>
-      <c r="B61" s="33">
+      <c r="B61" s="23">
         <v>45716</v>
       </c>
       <c r="C61" t="s">
@@ -25789,10 +27662,10 @@
       <c r="D61" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="24" t="s">
+      <c r="E61" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F61" s="24" t="s">
+      <c r="F61" s="16" t="s">
         <v>128</v>
       </c>
       <c r="G61" t="s">
@@ -25807,7 +27680,7 @@
       <c r="A62" t="s">
         <v>49</v>
       </c>
-      <c r="B62" s="33">
+      <c r="B62" s="23">
         <v>45780</v>
       </c>
       <c r="C62" t="s">
@@ -25816,10 +27689,10 @@
       <c r="D62" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="E62" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F62" s="24" t="s">
+      <c r="F62" s="16" t="s">
         <v>44</v>
       </c>
       <c r="G62" t="s">
@@ -25834,7 +27707,7 @@
       <c r="A63" t="s">
         <v>129</v>
       </c>
-      <c r="B63" s="33">
+      <c r="B63" s="23">
         <v>46070</v>
       </c>
       <c r="C63" t="s">
@@ -25843,10 +27716,10 @@
       <c r="D63" t="s">
         <v>9</v>
       </c>
-      <c r="E63" s="24" t="s">
+      <c r="E63" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F63" s="24" t="s">
+      <c r="F63" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
@@ -25861,7 +27734,7 @@
       <c r="A64" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="33">
+      <c r="B64" s="23">
         <v>46057</v>
       </c>
       <c r="C64" t="s">
@@ -25870,10 +27743,10 @@
       <c r="D64" t="s">
         <v>18</v>
       </c>
-      <c r="E64" s="24">
+      <c r="E64" s="16">
         <v>0.58680555555555558</v>
       </c>
-      <c r="F64" s="24" t="s">
+      <c r="F64" s="16" t="s">
         <v>44</v>
       </c>
       <c r="G64" t="s">
@@ -25888,7 +27761,7 @@
       <c r="A65" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="33">
+      <c r="B65" s="23">
         <v>45826</v>
       </c>
       <c r="C65" t="s">
@@ -25897,10 +27770,10 @@
       <c r="D65" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F65" s="24">
+      <c r="F65" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G65" t="s">
@@ -25915,7 +27788,7 @@
       <c r="A66" t="s">
         <v>131</v>
       </c>
-      <c r="B66" s="33">
+      <c r="B66" s="23">
         <v>45789</v>
       </c>
       <c r="C66" t="s">
@@ -25924,10 +27797,10 @@
       <c r="D66" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F66" s="24" t="s">
+      <c r="F66" s="16" t="s">
         <v>32</v>
       </c>
       <c r="G66" t="s">
@@ -25942,7 +27815,7 @@
       <c r="A67" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="33">
+      <c r="B67" s="23">
         <v>45677</v>
       </c>
       <c r="C67" t="s">
@@ -25951,10 +27824,10 @@
       <c r="D67" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F67" s="24" t="s">
+      <c r="F67" s="16" t="s">
         <v>133</v>
       </c>
       <c r="G67" t="s">
@@ -25969,7 +27842,7 @@
       <c r="A68" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="33">
+      <c r="B68" s="23">
         <v>45995</v>
       </c>
       <c r="C68" t="s">
@@ -25978,10 +27851,10 @@
       <c r="D68" t="s">
         <v>9</v>
       </c>
-      <c r="E68" s="24" t="s">
+      <c r="E68" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F68" s="24">
+      <c r="F68" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G68" t="s">
@@ -25996,7 +27869,7 @@
       <c r="A69" t="s">
         <v>84</v>
       </c>
-      <c r="B69" s="33">
+      <c r="B69" s="23">
         <v>46158</v>
       </c>
       <c r="C69" t="s">
@@ -26005,10 +27878,10 @@
       <c r="D69" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="24" t="s">
+      <c r="E69" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F69" s="24" t="s">
+      <c r="F69" s="16" t="s">
         <v>136</v>
       </c>
       <c r="G69" t="s">
@@ -26023,7 +27896,7 @@
       <c r="A70" t="s">
         <v>29</v>
       </c>
-      <c r="B70" s="33">
+      <c r="B70" s="23">
         <v>46097</v>
       </c>
       <c r="C70" t="s">
@@ -26032,10 +27905,10 @@
       <c r="D70" t="s">
         <v>18</v>
       </c>
-      <c r="E70" s="24" t="s">
+      <c r="E70" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="F70" s="24" t="s">
+      <c r="F70" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G70" t="s">
@@ -26050,7 +27923,7 @@
       <c r="A71" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="33">
+      <c r="B71" s="23">
         <v>46169</v>
       </c>
       <c r="C71" t="s">
@@ -26059,10 +27932,10 @@
       <c r="D71" t="s">
         <v>9</v>
       </c>
-      <c r="E71" s="24" t="s">
+      <c r="E71" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F71" s="24" t="s">
+      <c r="F71" s="16" t="s">
         <v>142</v>
       </c>
       <c r="G71" t="s">
@@ -26077,7 +27950,7 @@
       <c r="A72" t="s">
         <v>62</v>
       </c>
-      <c r="B72" s="33">
+      <c r="B72" s="23">
         <v>46155</v>
       </c>
       <c r="C72" t="s">
@@ -26086,10 +27959,10 @@
       <c r="D72" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="24" t="s">
+      <c r="E72" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F72" s="24" t="s">
+      <c r="F72" s="16" t="s">
         <v>143</v>
       </c>
       <c r="G72" t="s">
@@ -26104,7 +27977,7 @@
       <c r="A73" t="s">
         <v>62</v>
       </c>
-      <c r="B73" s="33">
+      <c r="B73" s="23">
         <v>45760</v>
       </c>
       <c r="C73" t="s">
@@ -26113,10 +27986,10 @@
       <c r="D73" t="s">
         <v>9</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="E73" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F73" s="24" t="s">
+      <c r="F73" s="16" t="s">
         <v>72</v>
       </c>
       <c r="G73" t="s">
@@ -26131,7 +28004,7 @@
       <c r="A74" t="s">
         <v>13</v>
       </c>
-      <c r="B74" s="33">
+      <c r="B74" s="23">
         <v>45771</v>
       </c>
       <c r="C74" t="s">
@@ -26140,10 +28013,10 @@
       <c r="D74" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="24">
+      <c r="E74" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F74" s="24" t="s">
+      <c r="F74" s="16" t="s">
         <v>128</v>
       </c>
       <c r="G74" t="s">
@@ -26158,7 +28031,7 @@
       <c r="A75" t="s">
         <v>57</v>
       </c>
-      <c r="B75" s="33">
+      <c r="B75" s="23">
         <v>46181</v>
       </c>
       <c r="C75" t="s">
@@ -26167,10 +28040,10 @@
       <c r="D75" t="s">
         <v>9</v>
       </c>
-      <c r="E75" s="24" t="s">
+      <c r="E75" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F75" s="24" t="s">
+      <c r="F75" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G75" t="s">
@@ -26185,7 +28058,7 @@
       <c r="A76" t="s">
         <v>42</v>
       </c>
-      <c r="B76" s="33">
+      <c r="B76" s="23">
         <v>45733</v>
       </c>
       <c r="C76" t="s">
@@ -26194,10 +28067,10 @@
       <c r="D76" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="24" t="s">
+      <c r="E76" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F76" s="24" t="s">
+      <c r="F76" s="16" t="s">
         <v>94</v>
       </c>
       <c r="G76" t="s">
@@ -26212,7 +28085,7 @@
       <c r="A77" t="s">
         <v>106</v>
       </c>
-      <c r="B77" s="33">
+      <c r="B77" s="23">
         <v>45944</v>
       </c>
       <c r="C77" t="s">
@@ -26221,10 +28094,10 @@
       <c r="D77" t="s">
         <v>9</v>
       </c>
-      <c r="E77" s="24" t="s">
+      <c r="E77" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F77" s="24" t="s">
+      <c r="F77" s="16" t="s">
         <v>146</v>
       </c>
       <c r="G77" t="s">
@@ -26239,7 +28112,7 @@
       <c r="A78" t="s">
         <v>13</v>
       </c>
-      <c r="B78" s="33">
+      <c r="B78" s="23">
         <v>46071</v>
       </c>
       <c r="C78" t="s">
@@ -26248,10 +28121,10 @@
       <c r="D78" t="s">
         <v>9</v>
       </c>
-      <c r="E78" s="24" t="s">
+      <c r="E78" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F78" s="24" t="s">
+      <c r="F78" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G78" t="s">
@@ -26266,7 +28139,7 @@
       <c r="A79" t="s">
         <v>80</v>
       </c>
-      <c r="B79" s="33">
+      <c r="B79" s="23">
         <v>45868</v>
       </c>
       <c r="C79" t="s">
@@ -26275,10 +28148,10 @@
       <c r="D79" t="s">
         <v>18</v>
       </c>
-      <c r="E79" s="24" t="s">
+      <c r="E79" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F79" s="24" t="s">
+      <c r="F79" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G79" t="s">
@@ -26293,7 +28166,7 @@
       <c r="A80" t="s">
         <v>53</v>
       </c>
-      <c r="B80" s="33">
+      <c r="B80" s="23">
         <v>46199</v>
       </c>
       <c r="C80" t="s">
@@ -26302,10 +28175,10 @@
       <c r="D80" t="s">
         <v>9</v>
       </c>
-      <c r="E80" s="24" t="s">
+      <c r="E80" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F80" s="24" t="s">
+      <c r="F80" s="16" t="s">
         <v>91</v>
       </c>
       <c r="G80" t="s">
@@ -26320,7 +28193,7 @@
       <c r="A81" t="s">
         <v>147</v>
       </c>
-      <c r="B81" s="33">
+      <c r="B81" s="23">
         <v>45883</v>
       </c>
       <c r="C81" t="s">
@@ -26329,10 +28202,10 @@
       <c r="D81" t="s">
         <v>9</v>
       </c>
-      <c r="E81" s="24" t="s">
+      <c r="E81" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F81" s="24" t="s">
+      <c r="F81" s="16" t="s">
         <v>148</v>
       </c>
       <c r="G81" t="s">
@@ -26347,7 +28220,7 @@
       <c r="A82" t="s">
         <v>149</v>
       </c>
-      <c r="B82" s="33">
+      <c r="B82" s="23">
         <v>45776</v>
       </c>
       <c r="C82" t="s">
@@ -26356,10 +28229,10 @@
       <c r="D82" t="s">
         <v>18</v>
       </c>
-      <c r="E82" s="24" t="s">
+      <c r="E82" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F82" s="24" t="s">
+      <c r="F82" s="16" t="s">
         <v>32</v>
       </c>
       <c r="G82" t="s">
@@ -26374,7 +28247,7 @@
       <c r="A83" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="33">
+      <c r="B83" s="23">
         <v>46162</v>
       </c>
       <c r="C83" t="s">
@@ -26383,10 +28256,10 @@
       <c r="D83" t="s">
         <v>9</v>
       </c>
-      <c r="E83" s="24" t="s">
+      <c r="E83" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F83" s="24" t="s">
+      <c r="F83" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G83" t="s">
@@ -26401,7 +28274,7 @@
       <c r="A84" t="s">
         <v>76</v>
       </c>
-      <c r="B84" s="33">
+      <c r="B84" s="23">
         <v>46059</v>
       </c>
       <c r="C84" t="s">
@@ -26410,10 +28283,10 @@
       <c r="D84" t="s">
         <v>18</v>
       </c>
-      <c r="E84" s="24" t="s">
+      <c r="E84" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F84" s="24" t="s">
+      <c r="F84" s="16" t="s">
         <v>150</v>
       </c>
       <c r="G84" t="s">
@@ -26428,7 +28301,7 @@
       <c r="A85" t="s">
         <v>151</v>
       </c>
-      <c r="B85" s="33">
+      <c r="B85" s="23">
         <v>45878</v>
       </c>
       <c r="C85" t="s">
@@ -26437,10 +28310,10 @@
       <c r="D85" t="s">
         <v>9</v>
       </c>
-      <c r="E85" s="24" t="s">
+      <c r="E85" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F85" s="24" t="s">
+      <c r="F85" s="16" t="s">
         <v>153</v>
       </c>
       <c r="G85" t="s">
@@ -26455,7 +28328,7 @@
       <c r="A86" t="s">
         <v>53</v>
       </c>
-      <c r="B86" s="33">
+      <c r="B86" s="23">
         <v>45748</v>
       </c>
       <c r="C86" t="s">
@@ -26464,10 +28337,10 @@
       <c r="D86" t="s">
         <v>9</v>
       </c>
-      <c r="E86" s="24" t="s">
+      <c r="E86" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F86" s="24">
+      <c r="F86" s="16">
         <v>0.9291666666666667</v>
       </c>
       <c r="G86" t="s">
@@ -26482,7 +28355,7 @@
       <c r="A87" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="33">
+      <c r="B87" s="23">
         <v>45660</v>
       </c>
       <c r="C87" t="s">
@@ -26491,10 +28364,10 @@
       <c r="D87" t="s">
         <v>9</v>
       </c>
-      <c r="E87" s="24" t="s">
+      <c r="E87" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F87" s="24" t="s">
+      <c r="F87" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G87" t="s">
@@ -26509,7 +28382,7 @@
       <c r="A88" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="33">
+      <c r="B88" s="23">
         <v>46066</v>
       </c>
       <c r="C88" t="s">
@@ -26518,10 +28391,10 @@
       <c r="D88" t="s">
         <v>9</v>
       </c>
-      <c r="E88" s="24" t="s">
+      <c r="E88" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F88" s="24" t="s">
+      <c r="F88" s="16" t="s">
         <v>98</v>
       </c>
       <c r="G88" t="s">
@@ -26536,7 +28409,7 @@
       <c r="A89" t="s">
         <v>49</v>
       </c>
-      <c r="B89" s="33">
+      <c r="B89" s="23">
         <v>45858</v>
       </c>
       <c r="C89" t="s">
@@ -26545,10 +28418,10 @@
       <c r="D89" t="s">
         <v>9</v>
       </c>
-      <c r="E89" s="24" t="s">
+      <c r="E89" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F89" s="24" t="s">
+      <c r="F89" s="16" t="s">
         <v>155</v>
       </c>
       <c r="G89" t="s">
@@ -26563,7 +28436,7 @@
       <c r="A90" t="s">
         <v>156</v>
       </c>
-      <c r="B90" s="33">
+      <c r="B90" s="23">
         <v>46049</v>
       </c>
       <c r="C90" t="s">
@@ -26572,10 +28445,10 @@
       <c r="D90" t="s">
         <v>18</v>
       </c>
-      <c r="E90" s="24" t="s">
+      <c r="E90" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="F90" s="24" t="s">
+      <c r="F90" s="16" t="s">
         <v>72</v>
       </c>
       <c r="G90" t="s">
@@ -26590,7 +28463,7 @@
       <c r="A91" t="s">
         <v>141</v>
       </c>
-      <c r="B91" s="33">
+      <c r="B91" s="23">
         <v>46221</v>
       </c>
       <c r="C91" t="s">
@@ -26599,10 +28472,10 @@
       <c r="D91" t="s">
         <v>9</v>
       </c>
-      <c r="E91" s="24" t="s">
+      <c r="E91" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F91" s="24" t="s">
+      <c r="F91" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G91" t="s">
@@ -26617,7 +28490,7 @@
       <c r="A92" t="s">
         <v>7</v>
       </c>
-      <c r="B92" s="33">
+      <c r="B92" s="23">
         <v>46172</v>
       </c>
       <c r="C92" t="s">
@@ -26626,10 +28499,10 @@
       <c r="D92" t="s">
         <v>18</v>
       </c>
-      <c r="E92" s="24" t="s">
+      <c r="E92" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F92" s="24" t="s">
+      <c r="F92" s="16" t="s">
         <v>133</v>
       </c>
       <c r="G92" t="s">
@@ -26644,7 +28517,7 @@
       <c r="A93" t="s">
         <v>78</v>
       </c>
-      <c r="B93" s="33">
+      <c r="B93" s="23">
         <v>46110</v>
       </c>
       <c r="C93" t="s">
@@ -26653,10 +28526,10 @@
       <c r="D93" t="s">
         <v>9</v>
       </c>
-      <c r="E93" s="24">
+      <c r="E93" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F93" s="24" t="s">
+      <c r="F93" s="16" t="s">
         <v>150</v>
       </c>
       <c r="G93" t="s">
@@ -26671,7 +28544,7 @@
       <c r="A94" t="s">
         <v>118</v>
       </c>
-      <c r="B94" s="33">
+      <c r="B94" s="23">
         <v>45847</v>
       </c>
       <c r="C94" t="s">
@@ -26680,10 +28553,10 @@
       <c r="D94" t="s">
         <v>18</v>
       </c>
-      <c r="E94" s="24" t="s">
+      <c r="E94" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F94" s="24" t="s">
+      <c r="F94" s="16" t="s">
         <v>143</v>
       </c>
       <c r="G94" t="s">
@@ -26698,7 +28571,7 @@
       <c r="A95" t="s">
         <v>71</v>
       </c>
-      <c r="B95" s="33">
+      <c r="B95" s="23">
         <v>46152</v>
       </c>
       <c r="C95" t="s">
@@ -26707,10 +28580,10 @@
       <c r="D95" t="s">
         <v>9</v>
       </c>
-      <c r="E95" s="24" t="s">
+      <c r="E95" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F95" s="24" t="s">
+      <c r="F95" s="16" t="s">
         <v>117</v>
       </c>
       <c r="G95" t="s">
@@ -26725,7 +28598,7 @@
       <c r="A96" t="s">
         <v>121</v>
       </c>
-      <c r="B96" s="33">
+      <c r="B96" s="23">
         <v>45852</v>
       </c>
       <c r="C96" t="s">
@@ -26734,10 +28607,10 @@
       <c r="D96" t="s">
         <v>9</v>
       </c>
-      <c r="E96" s="24" t="s">
+      <c r="E96" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="F96" s="24" t="s">
+      <c r="F96" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G96" t="s">
@@ -26752,7 +28625,7 @@
       <c r="A97" t="s">
         <v>114</v>
       </c>
-      <c r="B97" s="33">
+      <c r="B97" s="23">
         <v>46227</v>
       </c>
       <c r="C97" t="s">
@@ -26761,10 +28634,10 @@
       <c r="D97" t="s">
         <v>18</v>
       </c>
-      <c r="E97" s="24" t="s">
+      <c r="E97" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="F97" s="24" t="s">
+      <c r="F97" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G97" t="s">
@@ -26779,7 +28652,7 @@
       <c r="A98" t="s">
         <v>57</v>
       </c>
-      <c r="B98" s="33">
+      <c r="B98" s="23">
         <v>46068</v>
       </c>
       <c r="C98" t="s">
@@ -26788,10 +28661,10 @@
       <c r="D98" t="s">
         <v>18</v>
       </c>
-      <c r="E98" s="24" t="s">
+      <c r="E98" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F98" s="24" t="s">
+      <c r="F98" s="16" t="s">
         <v>88</v>
       </c>
       <c r="G98" t="s">
@@ -26806,7 +28679,7 @@
       <c r="A99" t="s">
         <v>160</v>
       </c>
-      <c r="B99" s="33">
+      <c r="B99" s="23">
         <v>46154</v>
       </c>
       <c r="C99" t="s">
@@ -26815,10 +28688,10 @@
       <c r="D99" t="s">
         <v>18</v>
       </c>
-      <c r="E99" s="24">
+      <c r="E99" s="16">
         <v>0.58680555555555558</v>
       </c>
-      <c r="F99" s="24" t="s">
+      <c r="F99" s="16" t="s">
         <v>61</v>
       </c>
       <c r="G99" t="s">
@@ -26833,7 +28706,7 @@
       <c r="A100" t="s">
         <v>73</v>
       </c>
-      <c r="B100" s="33">
+      <c r="B100" s="23">
         <v>46061</v>
       </c>
       <c r="C100" t="s">
@@ -26842,10 +28715,10 @@
       <c r="D100" t="s">
         <v>9</v>
       </c>
-      <c r="E100" s="24" t="s">
+      <c r="E100" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F100" s="24" t="s">
+      <c r="F100" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G100" t="s">
@@ -26860,7 +28733,7 @@
       <c r="A101" t="s">
         <v>39</v>
       </c>
-      <c r="B101" s="33">
+      <c r="B101" s="23">
         <v>45699</v>
       </c>
       <c r="C101" t="s">
@@ -26869,10 +28742,10 @@
       <c r="D101" t="s">
         <v>9</v>
       </c>
-      <c r="E101" s="24" t="s">
+      <c r="E101" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F101" s="24" t="s">
+      <c r="F101" s="16" t="s">
         <v>161</v>
       </c>
       <c r="G101" t="s">
@@ -26887,7 +28760,7 @@
       <c r="A102" t="s">
         <v>156</v>
       </c>
-      <c r="B102" s="33">
+      <c r="B102" s="23">
         <v>46114</v>
       </c>
       <c r="C102" t="s">
@@ -26896,10 +28769,10 @@
       <c r="D102" t="s">
         <v>18</v>
       </c>
-      <c r="E102" s="24" t="s">
+      <c r="E102" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F102" s="24" t="s">
+      <c r="F102" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G102" t="s">
@@ -26914,7 +28787,7 @@
       <c r="A103" t="s">
         <v>162</v>
       </c>
-      <c r="B103" s="33">
+      <c r="B103" s="23">
         <v>45951</v>
       </c>
       <c r="C103" t="s">
@@ -26923,10 +28796,10 @@
       <c r="D103" t="s">
         <v>9</v>
       </c>
-      <c r="E103" s="24" t="s">
+      <c r="E103" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F103" s="24" t="s">
+      <c r="F103" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G103" t="s">
@@ -26941,7 +28814,7 @@
       <c r="A104" t="s">
         <v>13</v>
       </c>
-      <c r="B104" s="33">
+      <c r="B104" s="23">
         <v>46175</v>
       </c>
       <c r="C104" t="s">
@@ -26950,10 +28823,10 @@
       <c r="D104" t="s">
         <v>9</v>
       </c>
-      <c r="E104" s="24" t="s">
+      <c r="E104" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="F104" s="24">
+      <c r="F104" s="16">
         <v>0.9291666666666667</v>
       </c>
       <c r="G104" t="s">
@@ -26968,7 +28841,7 @@
       <c r="A105" t="s">
         <v>162</v>
       </c>
-      <c r="B105" s="33">
+      <c r="B105" s="23">
         <v>46006</v>
       </c>
       <c r="C105" t="s">
@@ -26977,10 +28850,10 @@
       <c r="D105" t="s">
         <v>9</v>
       </c>
-      <c r="E105" s="24" t="s">
+      <c r="E105" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F105" s="24" t="s">
+      <c r="F105" s="16" t="s">
         <v>165</v>
       </c>
       <c r="G105" t="s">
@@ -26995,7 +28868,7 @@
       <c r="A106" t="s">
         <v>112</v>
       </c>
-      <c r="B106" s="33">
+      <c r="B106" s="23">
         <v>46051</v>
       </c>
       <c r="C106" t="s">
@@ -27004,10 +28877,10 @@
       <c r="D106" t="s">
         <v>9</v>
       </c>
-      <c r="E106" s="24">
+      <c r="E106" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F106" s="24" t="s">
+      <c r="F106" s="16" t="s">
         <v>166</v>
       </c>
       <c r="G106" t="s">
@@ -27022,7 +28895,7 @@
       <c r="A107" t="s">
         <v>112</v>
       </c>
-      <c r="B107" s="33">
+      <c r="B107" s="23">
         <v>45670</v>
       </c>
       <c r="C107" t="s">
@@ -27031,10 +28904,10 @@
       <c r="D107" t="s">
         <v>9</v>
       </c>
-      <c r="E107" s="24" t="s">
+      <c r="E107" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F107" s="24" t="s">
+      <c r="F107" s="16" t="s">
         <v>117</v>
       </c>
       <c r="G107" t="s">
@@ -27049,7 +28922,7 @@
       <c r="A108" t="s">
         <v>106</v>
       </c>
-      <c r="B108" s="33">
+      <c r="B108" s="23">
         <v>46035</v>
       </c>
       <c r="C108" t="s">
@@ -27058,10 +28931,10 @@
       <c r="D108" t="s">
         <v>9</v>
       </c>
-      <c r="E108" s="24" t="s">
+      <c r="E108" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F108" s="24" t="s">
+      <c r="F108" s="16" t="s">
         <v>98</v>
       </c>
       <c r="G108" t="s">
@@ -27076,7 +28949,7 @@
       <c r="A109" t="s">
         <v>167</v>
       </c>
-      <c r="B109" s="33">
+      <c r="B109" s="23">
         <v>45812</v>
       </c>
       <c r="C109" t="s">
@@ -27085,10 +28958,10 @@
       <c r="D109" t="s">
         <v>9</v>
       </c>
-      <c r="E109" s="24" t="s">
+      <c r="E109" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F109" s="24" t="s">
+      <c r="F109" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G109" t="s">
@@ -27103,7 +28976,7 @@
       <c r="A110" t="s">
         <v>168</v>
       </c>
-      <c r="B110" s="33">
+      <c r="B110" s="23">
         <v>46007</v>
       </c>
       <c r="C110" t="s">
@@ -27112,10 +28985,10 @@
       <c r="D110" t="s">
         <v>9</v>
       </c>
-      <c r="E110" s="24" t="s">
+      <c r="E110" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F110" s="24" t="s">
+      <c r="F110" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G110" t="s">
@@ -27130,7 +29003,7 @@
       <c r="A111" t="s">
         <v>151</v>
       </c>
-      <c r="B111" s="33">
+      <c r="B111" s="23">
         <v>46015</v>
       </c>
       <c r="C111" t="s">
@@ -27139,10 +29012,10 @@
       <c r="D111" t="s">
         <v>9</v>
       </c>
-      <c r="E111" s="24" t="s">
+      <c r="E111" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="F111" s="24" t="s">
+      <c r="F111" s="16" t="s">
         <v>107</v>
       </c>
       <c r="G111" t="s">
@@ -27157,7 +29030,7 @@
       <c r="A112" t="s">
         <v>62</v>
       </c>
-      <c r="B112" s="33">
+      <c r="B112" s="23">
         <v>45863</v>
       </c>
       <c r="C112" t="s">
@@ -27166,10 +29039,10 @@
       <c r="D112" t="s">
         <v>9</v>
       </c>
-      <c r="E112" s="24" t="s">
+      <c r="E112" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="F112" s="24" t="s">
+      <c r="F112" s="16" t="s">
         <v>153</v>
       </c>
       <c r="G112" t="s">
@@ -27184,7 +29057,7 @@
       <c r="A113" t="s">
         <v>118</v>
       </c>
-      <c r="B113" s="33">
+      <c r="B113" s="23">
         <v>46029</v>
       </c>
       <c r="C113" t="s">
@@ -27193,10 +29066,10 @@
       <c r="D113" t="s">
         <v>9</v>
       </c>
-      <c r="E113" s="24" t="s">
+      <c r="E113" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F113" s="24" t="s">
+      <c r="F113" s="16" t="s">
         <v>98</v>
       </c>
       <c r="G113" t="s">
@@ -27211,7 +29084,7 @@
       <c r="A114" t="s">
         <v>172</v>
       </c>
-      <c r="B114" s="33">
+      <c r="B114" s="23">
         <v>45792</v>
       </c>
       <c r="C114" t="s">
@@ -27220,10 +29093,10 @@
       <c r="D114" t="s">
         <v>9</v>
       </c>
-      <c r="E114" s="24" t="s">
+      <c r="E114" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F114" s="24" t="s">
+      <c r="F114" s="16" t="s">
         <v>100</v>
       </c>
       <c r="G114" t="s">
@@ -27238,7 +29111,7 @@
       <c r="A115" t="s">
         <v>173</v>
       </c>
-      <c r="B115" s="33">
+      <c r="B115" s="23">
         <v>46025</v>
       </c>
       <c r="C115" t="s">
@@ -27247,10 +29120,10 @@
       <c r="D115" t="s">
         <v>18</v>
       </c>
-      <c r="E115" s="24" t="s">
+      <c r="E115" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F115" s="24" t="s">
+      <c r="F115" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G115" t="s">
@@ -27265,7 +29138,7 @@
       <c r="A116" t="s">
         <v>156</v>
       </c>
-      <c r="B116" s="33">
+      <c r="B116" s="23">
         <v>46213</v>
       </c>
       <c r="C116" t="s">
@@ -27274,10 +29147,10 @@
       <c r="D116" t="s">
         <v>9</v>
       </c>
-      <c r="E116" s="24" t="s">
+      <c r="E116" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F116" s="24" t="s">
+      <c r="F116" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G116" t="s">
@@ -27292,7 +29165,7 @@
       <c r="A117" t="s">
         <v>95</v>
       </c>
-      <c r="B117" s="33">
+      <c r="B117" s="23">
         <v>46227</v>
       </c>
       <c r="C117" t="s">
@@ -27301,10 +29174,10 @@
       <c r="D117" t="s">
         <v>9</v>
       </c>
-      <c r="E117" s="24" t="s">
+      <c r="E117" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F117" s="24" t="s">
+      <c r="F117" s="16" t="s">
         <v>88</v>
       </c>
       <c r="G117" t="s">
@@ -27319,7 +29192,7 @@
       <c r="A118" t="s">
         <v>51</v>
       </c>
-      <c r="B118" s="33">
+      <c r="B118" s="23">
         <v>45721</v>
       </c>
       <c r="C118" t="s">
@@ -27328,10 +29201,10 @@
       <c r="D118" t="s">
         <v>18</v>
       </c>
-      <c r="E118" s="24" t="s">
+      <c r="E118" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="F118" s="24" t="s">
+      <c r="F118" s="16" t="s">
         <v>100</v>
       </c>
       <c r="G118" t="s">
@@ -27346,7 +29219,7 @@
       <c r="A119" t="s">
         <v>147</v>
       </c>
-      <c r="B119" s="33">
+      <c r="B119" s="23">
         <v>45831</v>
       </c>
       <c r="C119" t="s">
@@ -27355,10 +29228,10 @@
       <c r="D119" t="s">
         <v>9</v>
       </c>
-      <c r="E119" s="24" t="s">
+      <c r="E119" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="F119" s="24" t="s">
+      <c r="F119" s="16" t="s">
         <v>116</v>
       </c>
       <c r="G119" t="s">
@@ -27373,7 +29246,7 @@
       <c r="A120" t="s">
         <v>53</v>
       </c>
-      <c r="B120" s="33">
+      <c r="B120" s="23">
         <v>45948</v>
       </c>
       <c r="C120" t="s">
@@ -27382,10 +29255,10 @@
       <c r="D120" t="s">
         <v>18</v>
       </c>
-      <c r="E120" s="24" t="s">
+      <c r="E120" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F120" s="24" t="s">
+      <c r="F120" s="16" t="s">
         <v>176</v>
       </c>
       <c r="G120" t="s">
@@ -27400,7 +29273,7 @@
       <c r="A121" t="s">
         <v>22</v>
       </c>
-      <c r="B121" s="33">
+      <c r="B121" s="23">
         <v>45675</v>
       </c>
       <c r="C121" t="s">
@@ -27409,10 +29282,10 @@
       <c r="D121" t="s">
         <v>9</v>
       </c>
-      <c r="E121" s="24" t="s">
+      <c r="E121" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F121" s="24" t="s">
+      <c r="F121" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G121" t="s">
@@ -27427,7 +29300,7 @@
       <c r="A122" t="s">
         <v>177</v>
       </c>
-      <c r="B122" s="33">
+      <c r="B122" s="23">
         <v>46139</v>
       </c>
       <c r="C122" t="s">
@@ -27436,10 +29309,10 @@
       <c r="D122" t="s">
         <v>18</v>
       </c>
-      <c r="E122" s="24" t="s">
+      <c r="E122" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F122" s="24" t="s">
+      <c r="F122" s="16" t="s">
         <v>107</v>
       </c>
       <c r="G122" t="s">
@@ -27454,7 +29327,7 @@
       <c r="A123" t="s">
         <v>70</v>
       </c>
-      <c r="B123" s="33">
+      <c r="B123" s="23">
         <v>46128</v>
       </c>
       <c r="C123" t="s">
@@ -27463,10 +29336,10 @@
       <c r="D123" t="s">
         <v>18</v>
       </c>
-      <c r="E123" s="24" t="s">
+      <c r="E123" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F123" s="24" t="s">
+      <c r="F123" s="16" t="s">
         <v>146</v>
       </c>
       <c r="G123" t="s">
@@ -27481,7 +29354,7 @@
       <c r="A124" t="s">
         <v>45</v>
       </c>
-      <c r="B124" s="33">
+      <c r="B124" s="23">
         <v>46166</v>
       </c>
       <c r="C124" t="s">
@@ -27490,10 +29363,10 @@
       <c r="D124" t="s">
         <v>18</v>
       </c>
-      <c r="E124" s="24" t="s">
+      <c r="E124" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F124" s="24" t="s">
+      <c r="F124" s="16" t="s">
         <v>178</v>
       </c>
       <c r="G124" t="s">
@@ -27508,7 +29381,7 @@
       <c r="A125" t="s">
         <v>95</v>
       </c>
-      <c r="B125" s="33">
+      <c r="B125" s="23">
         <v>45763</v>
       </c>
       <c r="C125" t="s">
@@ -27517,10 +29390,10 @@
       <c r="D125" t="s">
         <v>9</v>
       </c>
-      <c r="E125" s="24" t="s">
+      <c r="E125" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="F125" s="24" t="s">
+      <c r="F125" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G125" t="s">
@@ -27535,7 +29408,7 @@
       <c r="A126" t="s">
         <v>131</v>
       </c>
-      <c r="B126" s="33">
+      <c r="B126" s="23">
         <v>45847</v>
       </c>
       <c r="C126" t="s">
@@ -27544,10 +29417,10 @@
       <c r="D126" t="s">
         <v>9</v>
       </c>
-      <c r="E126" s="24" t="s">
+      <c r="E126" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F126" s="24" t="s">
+      <c r="F126" s="16" t="s">
         <v>176</v>
       </c>
       <c r="G126" t="s">
@@ -27562,7 +29435,7 @@
       <c r="A127" t="s">
         <v>13</v>
       </c>
-      <c r="B127" s="33">
+      <c r="B127" s="23">
         <v>45665</v>
       </c>
       <c r="C127" t="s">
@@ -27571,10 +29444,10 @@
       <c r="D127" t="s">
         <v>9</v>
       </c>
-      <c r="E127" s="24" t="s">
+      <c r="E127" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F127" s="24" t="s">
+      <c r="F127" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G127" t="s">
@@ -27589,7 +29462,7 @@
       <c r="A128" t="s">
         <v>56</v>
       </c>
-      <c r="B128" s="33">
+      <c r="B128" s="23">
         <v>46072</v>
       </c>
       <c r="C128" t="s">
@@ -27598,10 +29471,10 @@
       <c r="D128" t="s">
         <v>9</v>
       </c>
-      <c r="E128" s="24" t="s">
+      <c r="E128" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F128" s="24" t="s">
+      <c r="F128" s="16" t="s">
         <v>166</v>
       </c>
       <c r="G128" t="s">
@@ -27616,7 +29489,7 @@
       <c r="A129" t="s">
         <v>29</v>
       </c>
-      <c r="B129" s="33">
+      <c r="B129" s="23">
         <v>45857</v>
       </c>
       <c r="C129" t="s">
@@ -27625,10 +29498,10 @@
       <c r="D129" t="s">
         <v>9</v>
       </c>
-      <c r="E129" s="24" t="s">
+      <c r="E129" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F129" s="24" t="s">
+      <c r="F129" s="16" t="s">
         <v>140</v>
       </c>
       <c r="G129" t="s">
@@ -27643,7 +29516,7 @@
       <c r="A130" t="s">
         <v>149</v>
       </c>
-      <c r="B130" s="33">
+      <c r="B130" s="23">
         <v>45866</v>
       </c>
       <c r="C130" t="s">
@@ -27652,10 +29525,10 @@
       <c r="D130" t="s">
         <v>18</v>
       </c>
-      <c r="E130" s="24" t="s">
+      <c r="E130" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F130" s="24" t="s">
+      <c r="F130" s="16" t="s">
         <v>86</v>
       </c>
       <c r="G130" t="s">
@@ -27670,7 +29543,7 @@
       <c r="A131" t="s">
         <v>42</v>
       </c>
-      <c r="B131" s="33">
+      <c r="B131" s="23">
         <v>45786</v>
       </c>
       <c r="C131" t="s">
@@ -27679,10 +29552,10 @@
       <c r="D131" t="s">
         <v>18</v>
       </c>
-      <c r="E131" s="24" t="s">
+      <c r="E131" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F131" s="24" t="s">
+      <c r="F131" s="16" t="s">
         <v>143</v>
       </c>
       <c r="G131" t="s">
@@ -27697,7 +29570,7 @@
       <c r="A132" t="s">
         <v>80</v>
       </c>
-      <c r="B132" s="33">
+      <c r="B132" s="23">
         <v>45682</v>
       </c>
       <c r="C132" t="s">
@@ -27706,10 +29579,10 @@
       <c r="D132" t="s">
         <v>18</v>
       </c>
-      <c r="E132" s="24" t="s">
+      <c r="E132" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F132" s="24" t="s">
+      <c r="F132" s="16" t="s">
         <v>180</v>
       </c>
       <c r="G132" t="s">
@@ -27724,7 +29597,7 @@
       <c r="A133" t="s">
         <v>162</v>
       </c>
-      <c r="B133" s="33">
+      <c r="B133" s="23">
         <v>45908</v>
       </c>
       <c r="C133" t="s">
@@ -27733,10 +29606,10 @@
       <c r="D133" t="s">
         <v>9</v>
       </c>
-      <c r="E133" s="24">
+      <c r="E133" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F133" s="24" t="s">
+      <c r="F133" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G133" t="s">
@@ -27751,7 +29624,7 @@
       <c r="A134" t="s">
         <v>68</v>
       </c>
-      <c r="B134" s="33">
+      <c r="B134" s="23">
         <v>46197</v>
       </c>
       <c r="C134" t="s">
@@ -27760,10 +29633,10 @@
       <c r="D134" t="s">
         <v>9</v>
       </c>
-      <c r="E134" s="24" t="s">
+      <c r="E134" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="F134" s="24" t="s">
+      <c r="F134" s="16" t="s">
         <v>161</v>
       </c>
       <c r="G134" t="s">
@@ -27778,7 +29651,7 @@
       <c r="A135" t="s">
         <v>105</v>
       </c>
-      <c r="B135" s="33">
+      <c r="B135" s="23">
         <v>45727</v>
       </c>
       <c r="C135" t="s">
@@ -27787,10 +29660,10 @@
       <c r="D135" t="s">
         <v>9</v>
       </c>
-      <c r="E135" s="24" t="s">
+      <c r="E135" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F135" s="24" t="s">
+      <c r="F135" s="16" t="s">
         <v>140</v>
       </c>
       <c r="G135" t="s">
@@ -27805,7 +29678,7 @@
       <c r="A136" t="s">
         <v>83</v>
       </c>
-      <c r="B136" s="33">
+      <c r="B136" s="23">
         <v>45736</v>
       </c>
       <c r="C136" t="s">
@@ -27814,10 +29687,10 @@
       <c r="D136" t="s">
         <v>18</v>
       </c>
-      <c r="E136" s="24" t="s">
+      <c r="E136" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F136" s="24" t="s">
+      <c r="F136" s="16" t="s">
         <v>182</v>
       </c>
       <c r="G136" t="s">
@@ -27832,7 +29705,7 @@
       <c r="A137" t="s">
         <v>183</v>
       </c>
-      <c r="B137" s="33">
+      <c r="B137" s="23">
         <v>45790</v>
       </c>
       <c r="C137" t="s">
@@ -27841,10 +29714,10 @@
       <c r="D137" t="s">
         <v>18</v>
       </c>
-      <c r="E137" s="24" t="s">
+      <c r="E137" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F137" s="24" t="s">
+      <c r="F137" s="16" t="s">
         <v>108</v>
       </c>
       <c r="G137" t="s">
@@ -27859,7 +29732,7 @@
       <c r="A138" t="s">
         <v>109</v>
       </c>
-      <c r="B138" s="33">
+      <c r="B138" s="23">
         <v>46202</v>
       </c>
       <c r="C138" t="s">
@@ -27868,10 +29741,10 @@
       <c r="D138" t="s">
         <v>9</v>
       </c>
-      <c r="E138" s="24" t="s">
+      <c r="E138" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F138" s="24" t="s">
+      <c r="F138" s="16" t="s">
         <v>69</v>
       </c>
       <c r="G138" t="s">
@@ -27886,7 +29759,7 @@
       <c r="A139" t="s">
         <v>57</v>
       </c>
-      <c r="B139" s="33">
+      <c r="B139" s="23">
         <v>45715</v>
       </c>
       <c r="C139" t="s">
@@ -27895,10 +29768,10 @@
       <c r="D139" t="s">
         <v>18</v>
       </c>
-      <c r="E139" s="24" t="s">
+      <c r="E139" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F139" s="24" t="s">
+      <c r="F139" s="16" t="s">
         <v>117</v>
       </c>
       <c r="G139" t="s">
@@ -27913,7 +29786,7 @@
       <c r="A140" t="s">
         <v>141</v>
       </c>
-      <c r="B140" s="33">
+      <c r="B140" s="23">
         <v>46183</v>
       </c>
       <c r="C140" t="s">
@@ -27922,10 +29795,10 @@
       <c r="D140" t="s">
         <v>18</v>
       </c>
-      <c r="E140" s="24" t="s">
+      <c r="E140" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F140" s="24" t="s">
+      <c r="F140" s="16" t="s">
         <v>176</v>
       </c>
       <c r="G140" t="s">
@@ -27940,7 +29813,7 @@
       <c r="A141" t="s">
         <v>49</v>
       </c>
-      <c r="B141" s="33">
+      <c r="B141" s="23">
         <v>45720</v>
       </c>
       <c r="C141" t="s">
@@ -27949,10 +29822,10 @@
       <c r="D141" t="s">
         <v>9</v>
       </c>
-      <c r="E141" s="24" t="s">
+      <c r="E141" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F141" s="24" t="s">
+      <c r="F141" s="16" t="s">
         <v>184</v>
       </c>
       <c r="G141" t="s">
@@ -27967,7 +29840,7 @@
       <c r="A142" t="s">
         <v>156</v>
       </c>
-      <c r="B142" s="33">
+      <c r="B142" s="23">
         <v>46200</v>
       </c>
       <c r="C142" t="s">
@@ -27976,10 +29849,10 @@
       <c r="D142" t="s">
         <v>9</v>
       </c>
-      <c r="E142" s="24" t="s">
+      <c r="E142" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="F142" s="24" t="s">
+      <c r="F142" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G142" t="s">
@@ -27994,7 +29867,7 @@
       <c r="A143" t="s">
         <v>187</v>
       </c>
-      <c r="B143" s="33">
+      <c r="B143" s="23">
         <v>46150</v>
       </c>
       <c r="C143" t="s">
@@ -28003,10 +29876,10 @@
       <c r="D143" t="s">
         <v>9</v>
       </c>
-      <c r="E143" s="24" t="s">
+      <c r="E143" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F143" s="24">
+      <c r="F143" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G143" t="s">
@@ -28021,7 +29894,7 @@
       <c r="A144" t="s">
         <v>25</v>
       </c>
-      <c r="B144" s="33">
+      <c r="B144" s="23">
         <v>45872</v>
       </c>
       <c r="C144" t="s">
@@ -28030,10 +29903,10 @@
       <c r="D144" t="s">
         <v>18</v>
       </c>
-      <c r="E144" s="24" t="s">
+      <c r="E144" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F144" s="24" t="s">
+      <c r="F144" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G144" t="s">
@@ -28048,7 +29921,7 @@
       <c r="A145" t="s">
         <v>167</v>
       </c>
-      <c r="B145" s="33">
+      <c r="B145" s="23">
         <v>45835</v>
       </c>
       <c r="C145" t="s">
@@ -28057,10 +29930,10 @@
       <c r="D145" t="s">
         <v>18</v>
       </c>
-      <c r="E145" s="24" t="s">
+      <c r="E145" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F145" s="24" t="s">
+      <c r="F145" s="16" t="s">
         <v>67</v>
       </c>
       <c r="G145" t="s">
@@ -28075,7 +29948,7 @@
       <c r="A146" t="s">
         <v>89</v>
       </c>
-      <c r="B146" s="33">
+      <c r="B146" s="23">
         <v>46155</v>
       </c>
       <c r="C146" t="s">
@@ -28084,10 +29957,10 @@
       <c r="D146" t="s">
         <v>9</v>
       </c>
-      <c r="E146" s="24" t="s">
+      <c r="E146" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F146" s="24" t="s">
+      <c r="F146" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G146" t="s">
@@ -28102,7 +29975,7 @@
       <c r="A147" t="s">
         <v>168</v>
       </c>
-      <c r="B147" s="33">
+      <c r="B147" s="23">
         <v>45982</v>
       </c>
       <c r="C147" t="s">
@@ -28111,10 +29984,10 @@
       <c r="D147" t="s">
         <v>9</v>
       </c>
-      <c r="E147" s="24" t="s">
+      <c r="E147" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="F147" s="24" t="s">
+      <c r="F147" s="16" t="s">
         <v>190</v>
       </c>
       <c r="G147" t="s">
@@ -28129,7 +30002,7 @@
       <c r="A148" t="s">
         <v>80</v>
       </c>
-      <c r="B148" s="33">
+      <c r="B148" s="23">
         <v>45874</v>
       </c>
       <c r="C148" t="s">
@@ -28138,10 +30011,10 @@
       <c r="D148" t="s">
         <v>9</v>
       </c>
-      <c r="E148" s="24" t="s">
+      <c r="E148" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F148" s="24" t="s">
+      <c r="F148" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G148" t="s">
@@ -28156,7 +30029,7 @@
       <c r="A149" t="s">
         <v>68</v>
       </c>
-      <c r="B149" s="33">
+      <c r="B149" s="23">
         <v>45740</v>
       </c>
       <c r="C149" t="s">
@@ -28165,10 +30038,10 @@
       <c r="D149" t="s">
         <v>9</v>
       </c>
-      <c r="E149" s="24">
+      <c r="E149" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F149" s="24" t="s">
+      <c r="F149" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G149" t="s">
@@ -28183,7 +30056,7 @@
       <c r="A150" t="s">
         <v>183</v>
       </c>
-      <c r="B150" s="33">
+      <c r="B150" s="23">
         <v>45891</v>
       </c>
       <c r="C150" t="s">
@@ -28192,10 +30065,10 @@
       <c r="D150" t="s">
         <v>9</v>
       </c>
-      <c r="E150" s="24" t="s">
+      <c r="E150" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F150" s="24" t="s">
+      <c r="F150" s="16" t="s">
         <v>190</v>
       </c>
       <c r="G150" t="s">
@@ -28210,7 +30083,7 @@
       <c r="A151" t="s">
         <v>105</v>
       </c>
-      <c r="B151" s="33">
+      <c r="B151" s="23">
         <v>45847</v>
       </c>
       <c r="C151" t="s">
@@ -28219,10 +30092,10 @@
       <c r="D151" t="s">
         <v>9</v>
       </c>
-      <c r="E151" s="24" t="s">
+      <c r="E151" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="F151" s="24" t="s">
+      <c r="F151" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G151" t="s">
@@ -28237,7 +30110,7 @@
       <c r="A152" t="s">
         <v>192</v>
       </c>
-      <c r="B152" s="33">
+      <c r="B152" s="23">
         <v>46177</v>
       </c>
       <c r="C152" t="s">
@@ -28246,10 +30119,10 @@
       <c r="D152" t="s">
         <v>9</v>
       </c>
-      <c r="E152" s="24" t="s">
+      <c r="E152" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F152" s="24">
+      <c r="F152" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G152" t="s">
@@ -28264,7 +30137,7 @@
       <c r="A153" t="s">
         <v>162</v>
       </c>
-      <c r="B153" s="33">
+      <c r="B153" s="23">
         <v>45933</v>
       </c>
       <c r="C153" t="s">
@@ -28273,10 +30146,10 @@
       <c r="D153" t="s">
         <v>9</v>
       </c>
-      <c r="E153" s="24" t="s">
+      <c r="E153" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F153" s="24" t="s">
+      <c r="F153" s="16" t="s">
         <v>161</v>
       </c>
       <c r="G153" t="s">
@@ -28291,7 +30164,7 @@
       <c r="A154" t="s">
         <v>34</v>
       </c>
-      <c r="B154" s="33">
+      <c r="B154" s="23">
         <v>45762</v>
       </c>
       <c r="C154" t="s">
@@ -28300,10 +30173,10 @@
       <c r="D154" t="s">
         <v>9</v>
       </c>
-      <c r="E154" s="24" t="s">
+      <c r="E154" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F154" s="24" t="s">
+      <c r="F154" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G154" t="s">
@@ -28318,7 +30191,7 @@
       <c r="A155" t="s">
         <v>132</v>
       </c>
-      <c r="B155" s="33">
+      <c r="B155" s="23">
         <v>45679</v>
       </c>
       <c r="C155" t="s">
@@ -28327,10 +30200,10 @@
       <c r="D155" t="s">
         <v>9</v>
       </c>
-      <c r="E155" s="24" t="s">
+      <c r="E155" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="F155" s="24" t="s">
+      <c r="F155" s="16" t="s">
         <v>194</v>
       </c>
       <c r="G155" t="s">
@@ -28345,7 +30218,7 @@
       <c r="A156" t="s">
         <v>196</v>
       </c>
-      <c r="B156" s="33">
+      <c r="B156" s="23">
         <v>45993</v>
       </c>
       <c r="C156" t="s">
@@ -28354,10 +30227,10 @@
       <c r="D156" t="s">
         <v>9</v>
       </c>
-      <c r="E156" s="24" t="s">
+      <c r="E156" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F156" s="24" t="s">
+      <c r="F156" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G156" t="s">
@@ -28372,7 +30245,7 @@
       <c r="A157" t="s">
         <v>187</v>
       </c>
-      <c r="B157" s="33">
+      <c r="B157" s="23">
         <v>45805</v>
       </c>
       <c r="C157" t="s">
@@ -28381,10 +30254,10 @@
       <c r="D157" t="s">
         <v>9</v>
       </c>
-      <c r="E157" s="24" t="s">
+      <c r="E157" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F157" s="24" t="s">
+      <c r="F157" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G157" t="s">
@@ -28399,7 +30272,7 @@
       <c r="A158" t="s">
         <v>197</v>
       </c>
-      <c r="B158" s="33">
+      <c r="B158" s="23">
         <v>46086</v>
       </c>
       <c r="C158" t="s">
@@ -28408,10 +30281,10 @@
       <c r="D158" t="s">
         <v>18</v>
       </c>
-      <c r="E158" s="24" t="s">
+      <c r="E158" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F158" s="24" t="s">
+      <c r="F158" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G158" t="s">
@@ -28426,7 +30299,7 @@
       <c r="A159" t="s">
         <v>113</v>
       </c>
-      <c r="B159" s="33">
+      <c r="B159" s="23">
         <v>46023</v>
       </c>
       <c r="C159" t="s">
@@ -28435,10 +30308,10 @@
       <c r="D159" t="s">
         <v>9</v>
       </c>
-      <c r="E159" s="24" t="s">
+      <c r="E159" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F159" s="24" t="s">
+      <c r="F159" s="16" t="s">
         <v>198</v>
       </c>
       <c r="G159" t="s">
@@ -28453,7 +30326,7 @@
       <c r="A160" t="s">
         <v>89</v>
       </c>
-      <c r="B160" s="33">
+      <c r="B160" s="23">
         <v>46121</v>
       </c>
       <c r="C160" t="s">
@@ -28462,10 +30335,10 @@
       <c r="D160" t="s">
         <v>9</v>
       </c>
-      <c r="E160" s="24" t="s">
+      <c r="E160" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F160" s="24" t="s">
+      <c r="F160" s="16" t="s">
         <v>184</v>
       </c>
       <c r="G160" t="s">
@@ -28480,7 +30353,7 @@
       <c r="A161" t="s">
         <v>78</v>
       </c>
-      <c r="B161" s="33">
+      <c r="B161" s="23">
         <v>46188</v>
       </c>
       <c r="C161" t="s">
@@ -28489,10 +30362,10 @@
       <c r="D161" t="s">
         <v>9</v>
       </c>
-      <c r="E161" s="24" t="s">
+      <c r="E161" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F161" s="24" t="s">
+      <c r="F161" s="16" t="s">
         <v>116</v>
       </c>
       <c r="G161" t="s">
@@ -28507,7 +30380,7 @@
       <c r="A162" t="s">
         <v>199</v>
       </c>
-      <c r="B162" s="33">
+      <c r="B162" s="23">
         <v>46057</v>
       </c>
       <c r="C162" t="s">
@@ -28516,10 +30389,10 @@
       <c r="D162" t="s">
         <v>18</v>
       </c>
-      <c r="E162" s="24" t="s">
+      <c r="E162" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F162" s="24" t="s">
+      <c r="F162" s="16" t="s">
         <v>161</v>
       </c>
       <c r="G162" t="s">
@@ -28534,7 +30407,7 @@
       <c r="A163" t="s">
         <v>93</v>
       </c>
-      <c r="B163" s="33">
+      <c r="B163" s="23">
         <v>45827</v>
       </c>
       <c r="C163" t="s">
@@ -28543,10 +30416,10 @@
       <c r="D163" t="s">
         <v>9</v>
       </c>
-      <c r="E163" s="24" t="s">
+      <c r="E163" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="F163" s="24" t="s">
+      <c r="F163" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G163" t="s">
@@ -28561,7 +30434,7 @@
       <c r="A164" t="s">
         <v>177</v>
       </c>
-      <c r="B164" s="33">
+      <c r="B164" s="23">
         <v>45880</v>
       </c>
       <c r="C164" t="s">
@@ -28570,10 +30443,10 @@
       <c r="D164" t="s">
         <v>9</v>
       </c>
-      <c r="E164" s="24" t="s">
+      <c r="E164" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F164" s="24" t="s">
+      <c r="F164" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G164" t="s">
@@ -28588,7 +30461,7 @@
       <c r="A165" t="s">
         <v>177</v>
       </c>
-      <c r="B165" s="33">
+      <c r="B165" s="23">
         <v>45811</v>
       </c>
       <c r="C165" t="s">
@@ -28597,10 +30470,10 @@
       <c r="D165" t="s">
         <v>9</v>
       </c>
-      <c r="E165" s="24" t="s">
+      <c r="E165" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="F165" s="24" t="s">
+      <c r="F165" s="16" t="s">
         <v>61</v>
       </c>
       <c r="G165" t="s">
@@ -28615,7 +30488,7 @@
       <c r="A166" t="s">
         <v>202</v>
       </c>
-      <c r="B166" s="33">
+      <c r="B166" s="23">
         <v>45998</v>
       </c>
       <c r="C166" t="s">
@@ -28624,10 +30497,10 @@
       <c r="D166" t="s">
         <v>9</v>
       </c>
-      <c r="E166" s="24" t="s">
+      <c r="E166" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F166" s="24" t="s">
+      <c r="F166" s="16" t="s">
         <v>117</v>
       </c>
       <c r="G166" t="s">
@@ -28642,7 +30515,7 @@
       <c r="A167" t="s">
         <v>34</v>
       </c>
-      <c r="B167" s="33">
+      <c r="B167" s="23">
         <v>45735</v>
       </c>
       <c r="C167" t="s">
@@ -28651,10 +30524,10 @@
       <c r="D167" t="s">
         <v>9</v>
       </c>
-      <c r="E167" s="24" t="s">
+      <c r="E167" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F167" s="24" t="s">
+      <c r="F167" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G167" t="s">
@@ -28669,7 +30542,7 @@
       <c r="A168" t="s">
         <v>177</v>
       </c>
-      <c r="B168" s="33">
+      <c r="B168" s="23">
         <v>46130</v>
       </c>
       <c r="C168" t="s">
@@ -28678,10 +30551,10 @@
       <c r="D168" t="s">
         <v>9</v>
       </c>
-      <c r="E168" s="24" t="s">
+      <c r="E168" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="F168" s="24" t="s">
+      <c r="F168" s="16" t="s">
         <v>115</v>
       </c>
       <c r="G168" t="s">
@@ -28696,7 +30569,7 @@
       <c r="A169" t="s">
         <v>203</v>
       </c>
-      <c r="B169" s="33">
+      <c r="B169" s="23">
         <v>45952</v>
       </c>
       <c r="C169" t="s">
@@ -28705,10 +30578,10 @@
       <c r="D169" t="s">
         <v>18</v>
       </c>
-      <c r="E169" s="24" t="s">
+      <c r="E169" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="F169" s="24" t="s">
+      <c r="F169" s="16" t="s">
         <v>69</v>
       </c>
       <c r="G169" t="s">
@@ -28723,7 +30596,7 @@
       <c r="A170" t="s">
         <v>25</v>
       </c>
-      <c r="B170" s="33">
+      <c r="B170" s="23">
         <v>46172</v>
       </c>
       <c r="C170" t="s">
@@ -28732,10 +30605,10 @@
       <c r="D170" t="s">
         <v>9</v>
       </c>
-      <c r="E170" s="24" t="s">
+      <c r="E170" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F170" s="24" t="s">
+      <c r="F170" s="16" t="s">
         <v>143</v>
       </c>
       <c r="G170" t="s">
@@ -28750,7 +30623,7 @@
       <c r="A171" t="s">
         <v>29</v>
       </c>
-      <c r="B171" s="33">
+      <c r="B171" s="23">
         <v>45931</v>
       </c>
       <c r="C171" t="s">
@@ -28759,10 +30632,10 @@
       <c r="D171" t="s">
         <v>9</v>
       </c>
-      <c r="E171" s="24" t="s">
+      <c r="E171" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F171" s="24" t="s">
+      <c r="F171" s="16" t="s">
         <v>69</v>
       </c>
       <c r="G171" t="s">
@@ -28777,7 +30650,7 @@
       <c r="A172" t="s">
         <v>103</v>
       </c>
-      <c r="B172" s="33">
+      <c r="B172" s="23">
         <v>46063</v>
       </c>
       <c r="C172" t="s">
@@ -28786,10 +30659,10 @@
       <c r="D172" t="s">
         <v>9</v>
       </c>
-      <c r="E172" s="24" t="s">
+      <c r="E172" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="F172" s="24" t="s">
+      <c r="F172" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G172" t="s">
@@ -28804,7 +30677,7 @@
       <c r="A173" t="s">
         <v>131</v>
       </c>
-      <c r="B173" s="33">
+      <c r="B173" s="23">
         <v>45774</v>
       </c>
       <c r="C173" t="s">
@@ -28813,10 +30686,10 @@
       <c r="D173" t="s">
         <v>9</v>
       </c>
-      <c r="E173" s="24">
+      <c r="E173" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F173" s="24" t="s">
+      <c r="F173" s="16" t="s">
         <v>32</v>
       </c>
       <c r="G173" t="s">
@@ -28831,7 +30704,7 @@
       <c r="A174" t="s">
         <v>127</v>
       </c>
-      <c r="B174" s="33">
+      <c r="B174" s="23">
         <v>45989</v>
       </c>
       <c r="C174" t="s">
@@ -28840,10 +30713,10 @@
       <c r="D174" t="s">
         <v>9</v>
       </c>
-      <c r="E174" s="24" t="s">
+      <c r="E174" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F174" s="24" t="s">
+      <c r="F174" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G174" t="s">
@@ -28858,7 +30731,7 @@
       <c r="A175" t="s">
         <v>131</v>
       </c>
-      <c r="B175" s="33">
+      <c r="B175" s="23">
         <v>45935</v>
       </c>
       <c r="C175" t="s">
@@ -28867,10 +30740,10 @@
       <c r="D175" t="s">
         <v>9</v>
       </c>
-      <c r="E175" s="24" t="s">
+      <c r="E175" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F175" s="24" t="s">
+      <c r="F175" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G175" t="s">
@@ -28885,7 +30758,7 @@
       <c r="A176" t="s">
         <v>68</v>
       </c>
-      <c r="B176" s="33">
+      <c r="B176" s="23">
         <v>45802</v>
       </c>
       <c r="C176" t="s">
@@ -28894,10 +30767,10 @@
       <c r="D176" t="s">
         <v>9</v>
       </c>
-      <c r="E176" s="24" t="s">
+      <c r="E176" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F176" s="24" t="s">
+      <c r="F176" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G176" t="s">
@@ -28912,7 +30785,7 @@
       <c r="A177" t="s">
         <v>205</v>
       </c>
-      <c r="B177" s="33">
+      <c r="B177" s="23">
         <v>46063</v>
       </c>
       <c r="C177" t="s">
@@ -28921,10 +30794,10 @@
       <c r="D177" t="s">
         <v>9</v>
       </c>
-      <c r="E177" s="24" t="s">
+      <c r="E177" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F177" s="24" t="s">
+      <c r="F177" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G177" t="s">
@@ -28939,7 +30812,7 @@
       <c r="A178" t="s">
         <v>22</v>
       </c>
-      <c r="B178" s="33">
+      <c r="B178" s="23">
         <v>46108</v>
       </c>
       <c r="C178" t="s">
@@ -28948,10 +30821,10 @@
       <c r="D178" t="s">
         <v>9</v>
       </c>
-      <c r="E178" s="24" t="s">
+      <c r="E178" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="F178" s="24" t="s">
+      <c r="F178" s="16" t="s">
         <v>155</v>
       </c>
       <c r="G178" t="s">
@@ -28966,7 +30839,7 @@
       <c r="A179" t="s">
         <v>85</v>
       </c>
-      <c r="B179" s="33">
+      <c r="B179" s="23">
         <v>45877</v>
       </c>
       <c r="C179" t="s">
@@ -28975,10 +30848,10 @@
       <c r="D179" t="s">
         <v>9</v>
       </c>
-      <c r="E179" s="24" t="s">
+      <c r="E179" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F179" s="24">
+      <c r="F179" s="16">
         <v>0.9291666666666667</v>
       </c>
       <c r="G179" t="s">
@@ -28993,7 +30866,7 @@
       <c r="A180" t="s">
         <v>191</v>
       </c>
-      <c r="B180" s="33">
+      <c r="B180" s="23">
         <v>45998</v>
       </c>
       <c r="C180" t="s">
@@ -29002,10 +30875,10 @@
       <c r="D180" t="s">
         <v>9</v>
       </c>
-      <c r="E180" s="24" t="s">
+      <c r="E180" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="F180" s="24" t="s">
+      <c r="F180" s="16" t="s">
         <v>133</v>
       </c>
       <c r="G180" t="s">
@@ -29020,7 +30893,7 @@
       <c r="A181" t="s">
         <v>192</v>
       </c>
-      <c r="B181" s="33">
+      <c r="B181" s="23">
         <v>45911</v>
       </c>
       <c r="C181" t="s">
@@ -29029,10 +30902,10 @@
       <c r="D181" t="s">
         <v>9</v>
       </c>
-      <c r="E181" s="24" t="s">
+      <c r="E181" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F181" s="24" t="s">
+      <c r="F181" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G181" t="s">
@@ -29047,7 +30920,7 @@
       <c r="A182" t="s">
         <v>51</v>
       </c>
-      <c r="B182" s="33">
+      <c r="B182" s="23">
         <v>45865</v>
       </c>
       <c r="C182" t="s">
@@ -29056,10 +30929,10 @@
       <c r="D182" t="s">
         <v>9</v>
       </c>
-      <c r="E182" s="24" t="s">
+      <c r="E182" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F182" s="24" t="s">
+      <c r="F182" s="16" t="s">
         <v>72</v>
       </c>
       <c r="G182" t="s">
@@ -29074,7 +30947,7 @@
       <c r="A183" t="s">
         <v>110</v>
       </c>
-      <c r="B183" s="33">
+      <c r="B183" s="23">
         <v>45762</v>
       </c>
       <c r="C183" t="s">
@@ -29083,10 +30956,10 @@
       <c r="D183" t="s">
         <v>18</v>
       </c>
-      <c r="E183" s="24" t="s">
+      <c r="E183" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F183" s="24" t="s">
+      <c r="F183" s="16" t="s">
         <v>155</v>
       </c>
       <c r="G183" t="s">
@@ -29101,7 +30974,7 @@
       <c r="A184" t="s">
         <v>60</v>
       </c>
-      <c r="B184" s="33">
+      <c r="B184" s="23">
         <v>45972</v>
       </c>
       <c r="C184" t="s">
@@ -29110,10 +30983,10 @@
       <c r="D184" t="s">
         <v>18</v>
       </c>
-      <c r="E184" s="24" t="s">
+      <c r="E184" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F184" s="24" t="s">
+      <c r="F184" s="16" t="s">
         <v>190</v>
       </c>
       <c r="G184" t="s">
@@ -29128,7 +31001,7 @@
       <c r="A185" t="s">
         <v>168</v>
       </c>
-      <c r="B185" s="33">
+      <c r="B185" s="23">
         <v>46109</v>
       </c>
       <c r="C185" t="s">
@@ -29137,10 +31010,10 @@
       <c r="D185" t="s">
         <v>9</v>
       </c>
-      <c r="E185" s="24" t="s">
+      <c r="E185" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F185" s="24" t="s">
+      <c r="F185" s="16" t="s">
         <v>153</v>
       </c>
       <c r="G185" t="s">
@@ -29155,7 +31028,7 @@
       <c r="A186" t="s">
         <v>110</v>
       </c>
-      <c r="B186" s="33">
+      <c r="B186" s="23">
         <v>45667</v>
       </c>
       <c r="C186" t="s">
@@ -29164,10 +31037,10 @@
       <c r="D186" t="s">
         <v>9</v>
       </c>
-      <c r="E186" s="24" t="s">
+      <c r="E186" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F186" s="24" t="s">
+      <c r="F186" s="16" t="s">
         <v>55</v>
       </c>
       <c r="G186" t="s">
@@ -29182,7 +31055,7 @@
       <c r="A187" t="s">
         <v>177</v>
       </c>
-      <c r="B187" s="33">
+      <c r="B187" s="23">
         <v>46036</v>
       </c>
       <c r="C187" t="s">
@@ -29191,10 +31064,10 @@
       <c r="D187" t="s">
         <v>9</v>
       </c>
-      <c r="E187" s="24">
+      <c r="E187" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F187" s="24" t="s">
+      <c r="F187" s="16" t="s">
         <v>150</v>
       </c>
       <c r="G187" t="s">
@@ -29209,7 +31082,7 @@
       <c r="A188" t="s">
         <v>177</v>
       </c>
-      <c r="B188" s="33">
+      <c r="B188" s="23">
         <v>46032</v>
       </c>
       <c r="C188" t="s">
@@ -29218,10 +31091,10 @@
       <c r="D188" t="s">
         <v>9</v>
       </c>
-      <c r="E188" s="24" t="s">
+      <c r="E188" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F188" s="24" t="s">
+      <c r="F188" s="16" t="s">
         <v>120</v>
       </c>
       <c r="G188" t="s">
@@ -29236,7 +31109,7 @@
       <c r="A189" t="s">
         <v>92</v>
       </c>
-      <c r="B189" s="33">
+      <c r="B189" s="23">
         <v>45797</v>
       </c>
       <c r="C189" t="s">
@@ -29245,10 +31118,10 @@
       <c r="D189" t="s">
         <v>18</v>
       </c>
-      <c r="E189" s="24" t="s">
+      <c r="E189" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="F189" s="24" t="s">
+      <c r="F189" s="16" t="s">
         <v>100</v>
       </c>
       <c r="G189" t="s">
@@ -29263,7 +31136,7 @@
       <c r="A190" t="s">
         <v>103</v>
       </c>
-      <c r="B190" s="33">
+      <c r="B190" s="23">
         <v>45987</v>
       </c>
       <c r="C190" t="s">
@@ -29272,10 +31145,10 @@
       <c r="D190" t="s">
         <v>9</v>
       </c>
-      <c r="E190" s="24" t="s">
+      <c r="E190" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F190" s="24" t="s">
+      <c r="F190" s="16" t="s">
         <v>86</v>
       </c>
       <c r="G190" t="s">
@@ -29290,7 +31163,7 @@
       <c r="A191" t="s">
         <v>42</v>
       </c>
-      <c r="B191" s="33">
+      <c r="B191" s="23">
         <v>46096</v>
       </c>
       <c r="C191" t="s">
@@ -29299,10 +31172,10 @@
       <c r="D191" t="s">
         <v>18</v>
       </c>
-      <c r="E191" s="24" t="s">
+      <c r="E191" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F191" s="24" t="s">
+      <c r="F191" s="16" t="s">
         <v>146</v>
       </c>
       <c r="G191" t="s">
@@ -29317,7 +31190,7 @@
       <c r="A192" t="s">
         <v>80</v>
       </c>
-      <c r="B192" s="33">
+      <c r="B192" s="23">
         <v>46114</v>
       </c>
       <c r="C192" t="s">
@@ -29326,10 +31199,10 @@
       <c r="D192" t="s">
         <v>9</v>
       </c>
-      <c r="E192" s="24">
+      <c r="E192" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F192" s="24" t="s">
+      <c r="F192" s="16" t="s">
         <v>38</v>
       </c>
       <c r="G192" t="s">
@@ -29344,7 +31217,7 @@
       <c r="A193" t="s">
         <v>57</v>
       </c>
-      <c r="B193" s="33">
+      <c r="B193" s="23">
         <v>46111</v>
       </c>
       <c r="C193" t="s">
@@ -29353,10 +31226,10 @@
       <c r="D193" t="s">
         <v>18</v>
       </c>
-      <c r="E193" s="24" t="s">
+      <c r="E193" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F193" s="24" t="s">
+      <c r="F193" s="16" t="s">
         <v>44</v>
       </c>
       <c r="G193" t="s">
@@ -29371,7 +31244,7 @@
       <c r="A194" t="s">
         <v>151</v>
       </c>
-      <c r="B194" s="33">
+      <c r="B194" s="23">
         <v>46035</v>
       </c>
       <c r="C194" t="s">
@@ -29380,10 +31253,10 @@
       <c r="D194" t="s">
         <v>9</v>
       </c>
-      <c r="E194" s="24">
+      <c r="E194" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F194" s="24" t="s">
+      <c r="F194" s="16" t="s">
         <v>86</v>
       </c>
       <c r="G194" t="s">
@@ -29398,7 +31271,7 @@
       <c r="A195" t="s">
         <v>83</v>
       </c>
-      <c r="B195" s="33">
+      <c r="B195" s="23">
         <v>45976</v>
       </c>
       <c r="C195" t="s">
@@ -29407,10 +31280,10 @@
       <c r="D195" t="s">
         <v>18</v>
       </c>
-      <c r="E195" s="24" t="s">
+      <c r="E195" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="F195" s="24">
+      <c r="F195" s="16">
         <v>0.9291666666666667</v>
       </c>
       <c r="G195" t="s">
@@ -29425,7 +31298,7 @@
       <c r="A196" t="s">
         <v>147</v>
       </c>
-      <c r="B196" s="33">
+      <c r="B196" s="23">
         <v>46176</v>
       </c>
       <c r="C196" t="s">
@@ -29434,10 +31307,10 @@
       <c r="D196" t="s">
         <v>9</v>
       </c>
-      <c r="E196" s="24" t="s">
+      <c r="E196" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="F196" s="24" t="s">
+      <c r="F196" s="16" t="s">
         <v>140</v>
       </c>
       <c r="G196" t="s">
@@ -29452,7 +31325,7 @@
       <c r="A197" t="s">
         <v>106</v>
       </c>
-      <c r="B197" s="33">
+      <c r="B197" s="23">
         <v>46214</v>
       </c>
       <c r="C197" t="s">
@@ -29461,10 +31334,10 @@
       <c r="D197" t="s">
         <v>9</v>
       </c>
-      <c r="E197" s="24" t="s">
+      <c r="E197" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F197" s="24" t="s">
+      <c r="F197" s="16" t="s">
         <v>102</v>
       </c>
       <c r="G197" t="s">
@@ -29479,7 +31352,7 @@
       <c r="A198" t="s">
         <v>141</v>
       </c>
-      <c r="B198" s="33">
+      <c r="B198" s="23">
         <v>45820</v>
       </c>
       <c r="C198" t="s">
@@ -29488,10 +31361,10 @@
       <c r="D198" t="s">
         <v>18</v>
       </c>
-      <c r="E198" s="24" t="s">
+      <c r="E198" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="F198" s="24" t="s">
+      <c r="F198" s="16" t="s">
         <v>146</v>
       </c>
       <c r="G198" t="s">
@@ -29506,7 +31379,7 @@
       <c r="A199" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="33">
+      <c r="B199" s="23">
         <v>46167</v>
       </c>
       <c r="C199" t="s">
@@ -29515,10 +31388,10 @@
       <c r="D199" t="s">
         <v>18</v>
       </c>
-      <c r="E199" s="24" t="s">
+      <c r="E199" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="F199" s="24" t="s">
+      <c r="F199" s="16" t="s">
         <v>136</v>
       </c>
       <c r="G199" t="s">
@@ -29533,7 +31406,7 @@
       <c r="A200" t="s">
         <v>114</v>
       </c>
-      <c r="B200" s="33">
+      <c r="B200" s="23">
         <v>46183</v>
       </c>
       <c r="C200" t="s">
@@ -29542,10 +31415,10 @@
       <c r="D200" t="s">
         <v>18</v>
       </c>
-      <c r="E200" s="24" t="s">
+      <c r="E200" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F200" s="24" t="s">
+      <c r="F200" s="16" t="s">
         <v>155</v>
       </c>
       <c r="G200" t="s">
@@ -29560,7 +31433,7 @@
       <c r="A201" t="s">
         <v>49</v>
       </c>
-      <c r="B201" s="33">
+      <c r="B201" s="23">
         <v>45955</v>
       </c>
       <c r="C201" t="s">
@@ -29569,10 +31442,10 @@
       <c r="D201" t="s">
         <v>9</v>
       </c>
-      <c r="E201" s="24" t="s">
+      <c r="E201" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F201" s="24" t="s">
+      <c r="F201" s="16" t="s">
         <v>150</v>
       </c>
       <c r="G201" t="s">
@@ -29587,7 +31460,7 @@
       <c r="A202" t="s">
         <v>130</v>
       </c>
-      <c r="B202" s="33">
+      <c r="B202" s="23">
         <v>46066</v>
       </c>
       <c r="C202" t="s">
@@ -29596,10 +31469,10 @@
       <c r="D202" t="s">
         <v>9</v>
       </c>
-      <c r="E202" s="24" t="s">
+      <c r="E202" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F202" s="24" t="s">
+      <c r="F202" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G202" t="s">
@@ -29614,7 +31487,7 @@
       <c r="A203" t="s">
         <v>49</v>
       </c>
-      <c r="B203" s="33">
+      <c r="B203" s="23">
         <v>46011</v>
       </c>
       <c r="C203" t="s">
@@ -29623,10 +31496,10 @@
       <c r="D203" t="s">
         <v>9</v>
       </c>
-      <c r="E203" s="24" t="s">
+      <c r="E203" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F203" s="24" t="s">
+      <c r="F203" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G203" t="s">
@@ -29641,7 +31514,7 @@
       <c r="A204" t="s">
         <v>68</v>
       </c>
-      <c r="B204" s="33">
+      <c r="B204" s="23">
         <v>45668</v>
       </c>
       <c r="C204" t="s">
@@ -29650,10 +31523,10 @@
       <c r="D204" t="s">
         <v>9</v>
       </c>
-      <c r="E204" s="24" t="s">
+      <c r="E204" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F204" s="24" t="s">
+      <c r="F204" s="16" t="s">
         <v>211</v>
       </c>
       <c r="G204" t="s">
@@ -29668,7 +31541,7 @@
       <c r="A205" t="s">
         <v>60</v>
       </c>
-      <c r="B205" s="33">
+      <c r="B205" s="23">
         <v>46090</v>
       </c>
       <c r="C205" t="s">
@@ -29677,10 +31550,10 @@
       <c r="D205" t="s">
         <v>9</v>
       </c>
-      <c r="E205" s="24" t="s">
+      <c r="E205" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F205" s="24" t="s">
+      <c r="F205" s="16" t="s">
         <v>117</v>
       </c>
       <c r="G205" t="s">
@@ -29695,7 +31568,7 @@
       <c r="A206" t="s">
         <v>127</v>
       </c>
-      <c r="B206" s="33">
+      <c r="B206" s="23">
         <v>45753</v>
       </c>
       <c r="C206" t="s">
@@ -29704,10 +31577,10 @@
       <c r="D206" t="s">
         <v>9</v>
       </c>
-      <c r="E206" s="24" t="s">
+      <c r="E206" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F206" s="24" t="s">
+      <c r="F206" s="16" t="s">
         <v>55</v>
       </c>
       <c r="G206" t="s">
@@ -29722,7 +31595,7 @@
       <c r="A207" t="s">
         <v>131</v>
       </c>
-      <c r="B207" s="33">
+      <c r="B207" s="23">
         <v>46141</v>
       </c>
       <c r="C207" t="s">
@@ -29731,10 +31604,10 @@
       <c r="D207" t="s">
         <v>9</v>
       </c>
-      <c r="E207" s="24" t="s">
+      <c r="E207" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F207" s="24" t="s">
+      <c r="F207" s="16" t="s">
         <v>155</v>
       </c>
       <c r="G207" t="s">
@@ -29749,7 +31622,7 @@
       <c r="A208" t="s">
         <v>114</v>
       </c>
-      <c r="B208" s="33">
+      <c r="B208" s="23">
         <v>45891</v>
       </c>
       <c r="C208" t="s">
@@ -29758,10 +31631,10 @@
       <c r="D208" t="s">
         <v>18</v>
       </c>
-      <c r="E208" s="24" t="s">
+      <c r="E208" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F208" s="24">
+      <c r="F208" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G208" t="s">
@@ -29776,7 +31649,7 @@
       <c r="A209" t="s">
         <v>62</v>
       </c>
-      <c r="B209" s="33">
+      <c r="B209" s="23">
         <v>45671</v>
       </c>
       <c r="C209" t="s">
@@ -29785,10 +31658,10 @@
       <c r="D209" t="s">
         <v>18</v>
       </c>
-      <c r="E209" s="24" t="s">
+      <c r="E209" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F209" s="24" t="s">
+      <c r="F209" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G209" t="s">
@@ -29803,7 +31676,7 @@
       <c r="A210" t="s">
         <v>7</v>
       </c>
-      <c r="B210" s="33">
+      <c r="B210" s="23">
         <v>46054</v>
       </c>
       <c r="C210" t="s">
@@ -29812,10 +31685,10 @@
       <c r="D210" t="s">
         <v>9</v>
       </c>
-      <c r="E210" s="24" t="s">
+      <c r="E210" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F210" s="24">
+      <c r="F210" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G210" t="s">
@@ -29830,7 +31703,7 @@
       <c r="A211" t="s">
         <v>79</v>
       </c>
-      <c r="B211" s="33">
+      <c r="B211" s="23">
         <v>45763</v>
       </c>
       <c r="C211" t="s">
@@ -29839,10 +31712,10 @@
       <c r="D211" t="s">
         <v>18</v>
       </c>
-      <c r="E211" s="24">
+      <c r="E211" s="16">
         <v>0.58680555555555558</v>
       </c>
-      <c r="F211" s="24" t="s">
+      <c r="F211" s="16" t="s">
         <v>182</v>
       </c>
       <c r="G211" t="s">
@@ -29857,7 +31730,7 @@
       <c r="A212" t="s">
         <v>17</v>
       </c>
-      <c r="B212" s="33">
+      <c r="B212" s="23">
         <v>46006</v>
       </c>
       <c r="C212" t="s">
@@ -29866,10 +31739,10 @@
       <c r="D212" t="s">
         <v>9</v>
       </c>
-      <c r="E212" s="24" t="s">
+      <c r="E212" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F212" s="24" t="s">
+      <c r="F212" s="16" t="s">
         <v>178</v>
       </c>
       <c r="G212" t="s">
@@ -29884,7 +31757,7 @@
       <c r="A213" t="s">
         <v>39</v>
       </c>
-      <c r="B213" s="33">
+      <c r="B213" s="23">
         <v>45807</v>
       </c>
       <c r="C213" t="s">
@@ -29893,10 +31766,10 @@
       <c r="D213" t="s">
         <v>9</v>
       </c>
-      <c r="E213" s="24" t="s">
+      <c r="E213" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F213" s="24" t="s">
+      <c r="F213" s="16" t="s">
         <v>213</v>
       </c>
       <c r="G213" t="s">
@@ -29911,7 +31784,7 @@
       <c r="A214" t="s">
         <v>103</v>
       </c>
-      <c r="B214" s="33">
+      <c r="B214" s="23">
         <v>45703</v>
       </c>
       <c r="C214" t="s">
@@ -29920,10 +31793,10 @@
       <c r="D214" t="s">
         <v>18</v>
       </c>
-      <c r="E214" s="24" t="s">
+      <c r="E214" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F214" s="24" t="s">
+      <c r="F214" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G214" t="s">
@@ -29938,7 +31811,7 @@
       <c r="A215" t="s">
         <v>83</v>
       </c>
-      <c r="B215" s="33">
+      <c r="B215" s="23">
         <v>46212</v>
       </c>
       <c r="C215" t="s">
@@ -29947,10 +31820,10 @@
       <c r="D215" t="s">
         <v>9</v>
       </c>
-      <c r="E215" s="24" t="s">
+      <c r="E215" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F215" s="24" t="s">
+      <c r="F215" s="16" t="s">
         <v>67</v>
       </c>
       <c r="G215" t="s">
@@ -29965,7 +31838,7 @@
       <c r="A216" t="s">
         <v>106</v>
       </c>
-      <c r="B216" s="33">
+      <c r="B216" s="23">
         <v>45683</v>
       </c>
       <c r="C216" t="s">
@@ -29974,10 +31847,10 @@
       <c r="D216" t="s">
         <v>9</v>
       </c>
-      <c r="E216" s="24" t="s">
+      <c r="E216" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F216" s="24" t="s">
+      <c r="F216" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G216" t="s">
@@ -29992,7 +31865,7 @@
       <c r="A217" t="s">
         <v>79</v>
       </c>
-      <c r="B217" s="33">
+      <c r="B217" s="23">
         <v>45950</v>
       </c>
       <c r="C217" t="s">
@@ -30001,10 +31874,10 @@
       <c r="D217" t="s">
         <v>9</v>
       </c>
-      <c r="E217" s="24" t="s">
+      <c r="E217" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F217" s="24" t="s">
+      <c r="F217" s="16" t="s">
         <v>104</v>
       </c>
       <c r="G217" t="s">
@@ -30019,7 +31892,7 @@
       <c r="A218" t="s">
         <v>113</v>
       </c>
-      <c r="B218" s="33">
+      <c r="B218" s="23">
         <v>46004</v>
       </c>
       <c r="C218" t="s">
@@ -30028,10 +31901,10 @@
       <c r="D218" t="s">
         <v>9</v>
       </c>
-      <c r="E218" s="24" t="s">
+      <c r="E218" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F218" s="24" t="s">
+      <c r="F218" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G218" t="s">
@@ -30046,7 +31919,7 @@
       <c r="A219" t="s">
         <v>81</v>
       </c>
-      <c r="B219" s="33">
+      <c r="B219" s="23">
         <v>45859</v>
       </c>
       <c r="C219" t="s">
@@ -30055,10 +31928,10 @@
       <c r="D219" t="s">
         <v>9</v>
       </c>
-      <c r="E219" s="24" t="s">
+      <c r="E219" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="F219" s="24" t="s">
+      <c r="F219" s="16" t="s">
         <v>184</v>
       </c>
       <c r="G219" t="s">
@@ -30073,7 +31946,7 @@
       <c r="A220" t="s">
         <v>162</v>
       </c>
-      <c r="B220" s="33">
+      <c r="B220" s="23">
         <v>46095</v>
       </c>
       <c r="C220" t="s">
@@ -30082,10 +31955,10 @@
       <c r="D220" t="s">
         <v>18</v>
       </c>
-      <c r="E220" s="24" t="s">
+      <c r="E220" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F220" s="24" t="s">
+      <c r="F220" s="16" t="s">
         <v>143</v>
       </c>
       <c r="G220" t="s">
@@ -30100,7 +31973,7 @@
       <c r="A221" t="s">
         <v>39</v>
       </c>
-      <c r="B221" s="33">
+      <c r="B221" s="23">
         <v>45721</v>
       </c>
       <c r="C221" t="s">
@@ -30109,10 +31982,10 @@
       <c r="D221" t="s">
         <v>9</v>
       </c>
-      <c r="E221" s="24" t="s">
+      <c r="E221" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F221" s="24" t="s">
+      <c r="F221" s="16" t="s">
         <v>69</v>
       </c>
       <c r="G221" t="s">
@@ -30127,7 +32000,7 @@
       <c r="A222" t="s">
         <v>84</v>
       </c>
-      <c r="B222" s="33">
+      <c r="B222" s="23">
         <v>45832</v>
       </c>
       <c r="C222" t="s">
@@ -30136,10 +32009,10 @@
       <c r="D222" t="s">
         <v>9</v>
       </c>
-      <c r="E222" s="24" t="s">
+      <c r="E222" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F222" s="24" t="s">
+      <c r="F222" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G222" t="s">
@@ -30154,7 +32027,7 @@
       <c r="A223" t="s">
         <v>127</v>
       </c>
-      <c r="B223" s="33">
+      <c r="B223" s="23">
         <v>45680</v>
       </c>
       <c r="C223" t="s">
@@ -30163,10 +32036,10 @@
       <c r="D223" t="s">
         <v>9</v>
       </c>
-      <c r="E223" s="24" t="s">
+      <c r="E223" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F223" s="24" t="s">
+      <c r="F223" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G223" t="s">
@@ -30181,7 +32054,7 @@
       <c r="A224" t="s">
         <v>76</v>
       </c>
-      <c r="B224" s="33">
+      <c r="B224" s="23">
         <v>45798</v>
       </c>
       <c r="C224" t="s">
@@ -30190,10 +32063,10 @@
       <c r="D224" t="s">
         <v>9</v>
       </c>
-      <c r="E224" s="24" t="s">
+      <c r="E224" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F224" s="24" t="s">
+      <c r="F224" s="16" t="s">
         <v>104</v>
       </c>
       <c r="G224" t="s">
@@ -30208,7 +32081,7 @@
       <c r="A225" t="s">
         <v>173</v>
       </c>
-      <c r="B225" s="33">
+      <c r="B225" s="23">
         <v>46052</v>
       </c>
       <c r="C225" t="s">
@@ -30217,10 +32090,10 @@
       <c r="D225" t="s">
         <v>9</v>
       </c>
-      <c r="E225" s="24" t="s">
+      <c r="E225" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F225" s="24" t="s">
+      <c r="F225" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G225" t="s">
@@ -30235,7 +32108,7 @@
       <c r="A226" t="s">
         <v>95</v>
       </c>
-      <c r="B226" s="33">
+      <c r="B226" s="23">
         <v>45853</v>
       </c>
       <c r="C226" t="s">
@@ -30244,10 +32117,10 @@
       <c r="D226" t="s">
         <v>18</v>
       </c>
-      <c r="E226" s="24" t="s">
+      <c r="E226" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F226" s="24" t="s">
+      <c r="F226" s="16" t="s">
         <v>91</v>
       </c>
       <c r="G226" t="s">
@@ -30262,7 +32135,7 @@
       <c r="A227" t="s">
         <v>217</v>
       </c>
-      <c r="B227" s="33">
+      <c r="B227" s="23">
         <v>46049</v>
       </c>
       <c r="C227" t="s">
@@ -30271,10 +32144,10 @@
       <c r="D227" t="s">
         <v>9</v>
       </c>
-      <c r="E227" s="24" t="s">
+      <c r="E227" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F227" s="24" t="s">
+      <c r="F227" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G227" t="s">
@@ -30289,7 +32162,7 @@
       <c r="A228" t="s">
         <v>141</v>
       </c>
-      <c r="B228" s="33">
+      <c r="B228" s="23">
         <v>45847</v>
       </c>
       <c r="C228" t="s">
@@ -30298,10 +32171,10 @@
       <c r="D228" t="s">
         <v>18</v>
       </c>
-      <c r="E228" s="24">
+      <c r="E228" s="16">
         <v>0.58680555555555558</v>
       </c>
-      <c r="F228" s="24" t="s">
+      <c r="F228" s="16" t="s">
         <v>44</v>
       </c>
       <c r="G228" t="s">
@@ -30316,7 +32189,7 @@
       <c r="A229" t="s">
         <v>73</v>
       </c>
-      <c r="B229" s="33">
+      <c r="B229" s="23">
         <v>45838</v>
       </c>
       <c r="C229" t="s">
@@ -30325,10 +32198,10 @@
       <c r="D229" t="s">
         <v>18</v>
       </c>
-      <c r="E229" s="24" t="s">
+      <c r="E229" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F229" s="24" t="s">
+      <c r="F229" s="16" t="s">
         <v>32</v>
       </c>
       <c r="G229" t="s">
@@ -30343,7 +32216,7 @@
       <c r="A230" t="s">
         <v>29</v>
       </c>
-      <c r="B230" s="33">
+      <c r="B230" s="23">
         <v>45916</v>
       </c>
       <c r="C230" t="s">
@@ -30352,10 +32225,10 @@
       <c r="D230" t="s">
         <v>9</v>
       </c>
-      <c r="E230" s="24" t="s">
+      <c r="E230" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F230" s="24" t="s">
+      <c r="F230" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G230" t="s">
@@ -30370,7 +32243,7 @@
       <c r="A231" t="s">
         <v>160</v>
       </c>
-      <c r="B231" s="33">
+      <c r="B231" s="23">
         <v>45767</v>
       </c>
       <c r="C231" t="s">
@@ -30379,10 +32252,10 @@
       <c r="D231" t="s">
         <v>9</v>
       </c>
-      <c r="E231" s="24" t="s">
+      <c r="E231" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F231" s="24" t="s">
+      <c r="F231" s="16" t="s">
         <v>211</v>
       </c>
       <c r="G231" t="s">
@@ -30397,7 +32270,7 @@
       <c r="A232" t="s">
         <v>89</v>
       </c>
-      <c r="B232" s="33">
+      <c r="B232" s="23">
         <v>45780</v>
       </c>
       <c r="C232" t="s">
@@ -30406,10 +32279,10 @@
       <c r="D232" t="s">
         <v>9</v>
       </c>
-      <c r="E232" s="24">
+      <c r="E232" s="16">
         <v>0.33958333333333335</v>
       </c>
-      <c r="F232" s="24" t="s">
+      <c r="F232" s="16" t="s">
         <v>61</v>
       </c>
       <c r="G232" t="s">
@@ -30424,7 +32297,7 @@
       <c r="A233" t="s">
         <v>70</v>
       </c>
-      <c r="B233" s="33">
+      <c r="B233" s="23">
         <v>45868</v>
       </c>
       <c r="C233" t="s">
@@ -30433,10 +32306,10 @@
       <c r="D233" t="s">
         <v>9</v>
       </c>
-      <c r="E233" s="24" t="s">
+      <c r="E233" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F233" s="24" t="s">
+      <c r="F233" s="16" t="s">
         <v>67</v>
       </c>
       <c r="G233" t="s">
@@ -30451,7 +32324,7 @@
       <c r="A234" t="s">
         <v>79</v>
       </c>
-      <c r="B234" s="33">
+      <c r="B234" s="23">
         <v>45658</v>
       </c>
       <c r="C234" t="s">
@@ -30460,10 +32333,10 @@
       <c r="D234" t="s">
         <v>18</v>
       </c>
-      <c r="E234" s="24" t="s">
+      <c r="E234" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="F234" s="24" t="s">
+      <c r="F234" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G234" t="s">
@@ -30478,7 +32351,7 @@
       <c r="A235" t="s">
         <v>56</v>
       </c>
-      <c r="B235" s="33">
+      <c r="B235" s="23">
         <v>46122</v>
       </c>
       <c r="C235" t="s">
@@ -30487,10 +32360,10 @@
       <c r="D235" t="s">
         <v>9</v>
       </c>
-      <c r="E235" s="24" t="s">
+      <c r="E235" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="F235" s="24" t="s">
+      <c r="F235" s="16" t="s">
         <v>69</v>
       </c>
       <c r="G235" t="s">
@@ -30505,7 +32378,7 @@
       <c r="A236" t="s">
         <v>56</v>
       </c>
-      <c r="B236" s="33">
+      <c r="B236" s="23">
         <v>46191</v>
       </c>
       <c r="C236" t="s">
@@ -30514,10 +32387,10 @@
       <c r="D236" t="s">
         <v>18</v>
       </c>
-      <c r="E236" s="24">
+      <c r="E236" s="16">
         <v>0.58680555555555558</v>
       </c>
-      <c r="F236" s="24" t="s">
+      <c r="F236" s="16" t="s">
         <v>55</v>
       </c>
       <c r="G236" t="s">
@@ -30532,7 +32405,7 @@
       <c r="A237" t="s">
         <v>132</v>
       </c>
-      <c r="B237" s="33">
+      <c r="B237" s="23">
         <v>45873</v>
       </c>
       <c r="C237" t="s">
@@ -30541,10 +32414,10 @@
       <c r="D237" t="s">
         <v>9</v>
       </c>
-      <c r="E237" s="24" t="s">
+      <c r="E237" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="F237" s="24" t="s">
+      <c r="F237" s="16" t="s">
         <v>61</v>
       </c>
       <c r="G237" t="s">
@@ -30559,7 +32432,7 @@
       <c r="A238" t="s">
         <v>203</v>
       </c>
-      <c r="B238" s="33">
+      <c r="B238" s="23">
         <v>45750</v>
       </c>
       <c r="C238" t="s">
@@ -30568,10 +32441,10 @@
       <c r="D238" t="s">
         <v>9</v>
       </c>
-      <c r="E238" s="24" t="s">
+      <c r="E238" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="F238" s="24" t="s">
+      <c r="F238" s="16" t="s">
         <v>104</v>
       </c>
       <c r="G238" t="s">
@@ -30586,7 +32459,7 @@
       <c r="A239" t="s">
         <v>192</v>
       </c>
-      <c r="B239" s="33">
+      <c r="B239" s="23">
         <v>45982</v>
       </c>
       <c r="C239" t="s">
@@ -30595,10 +32468,10 @@
       <c r="D239" t="s">
         <v>9</v>
       </c>
-      <c r="E239" s="24" t="s">
+      <c r="E239" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F239" s="24" t="s">
+      <c r="F239" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G239" t="s">
@@ -30613,7 +32486,7 @@
       <c r="A240" t="s">
         <v>42</v>
       </c>
-      <c r="B240" s="33">
+      <c r="B240" s="23">
         <v>45671</v>
       </c>
       <c r="C240" t="s">
@@ -30622,10 +32495,10 @@
       <c r="D240" t="s">
         <v>18</v>
       </c>
-      <c r="E240" s="24" t="s">
+      <c r="E240" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F240" s="24" t="s">
+      <c r="F240" s="16" t="s">
         <v>115</v>
       </c>
       <c r="G240" t="s">
@@ -30640,7 +32513,7 @@
       <c r="A241" t="s">
         <v>76</v>
       </c>
-      <c r="B241" s="33">
+      <c r="B241" s="23">
         <v>45823</v>
       </c>
       <c r="C241" t="s">
@@ -30649,10 +32522,10 @@
       <c r="D241" t="s">
         <v>9</v>
       </c>
-      <c r="E241" s="24" t="s">
+      <c r="E241" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="F241" s="24" t="s">
+      <c r="F241" s="16" t="s">
         <v>120</v>
       </c>
       <c r="G241" t="s">
@@ -30667,7 +32540,7 @@
       <c r="A242" t="s">
         <v>80</v>
       </c>
-      <c r="B242" s="33">
+      <c r="B242" s="23">
         <v>46189</v>
       </c>
       <c r="C242" t="s">
@@ -30676,10 +32549,10 @@
       <c r="D242" t="s">
         <v>18</v>
       </c>
-      <c r="E242" s="24" t="s">
+      <c r="E242" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F242" s="24" t="s">
+      <c r="F242" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G242" t="s">
@@ -30694,7 +32567,7 @@
       <c r="A243" t="s">
         <v>114</v>
       </c>
-      <c r="B243" s="33">
+      <c r="B243" s="23">
         <v>45895</v>
       </c>
       <c r="C243" t="s">
@@ -30703,10 +32576,10 @@
       <c r="D243" t="s">
         <v>9</v>
       </c>
-      <c r="E243" s="24" t="s">
+      <c r="E243" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F243" s="24" t="s">
+      <c r="F243" s="16" t="s">
         <v>94</v>
       </c>
       <c r="G243" t="s">
@@ -30721,7 +32594,7 @@
       <c r="A244" t="s">
         <v>25</v>
       </c>
-      <c r="B244" s="33">
+      <c r="B244" s="23">
         <v>45968</v>
       </c>
       <c r="C244" t="s">
@@ -30730,10 +32603,10 @@
       <c r="D244" t="s">
         <v>18</v>
       </c>
-      <c r="E244" s="24" t="s">
+      <c r="E244" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F244" s="24" t="s">
+      <c r="F244" s="16" t="s">
         <v>126</v>
       </c>
       <c r="G244" t="s">
@@ -30748,7 +32621,7 @@
       <c r="A245" t="s">
         <v>17</v>
       </c>
-      <c r="B245" s="33">
+      <c r="B245" s="23">
         <v>46042</v>
       </c>
       <c r="C245" t="s">
@@ -30757,10 +32630,10 @@
       <c r="D245" t="s">
         <v>9</v>
       </c>
-      <c r="E245" s="24" t="s">
+      <c r="E245" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F245" s="24" t="s">
+      <c r="F245" s="16" t="s">
         <v>120</v>
       </c>
       <c r="G245" t="s">
@@ -30775,7 +32648,7 @@
       <c r="A246" t="s">
         <v>87</v>
       </c>
-      <c r="B246" s="33">
+      <c r="B246" s="23">
         <v>45779</v>
       </c>
       <c r="C246" t="s">
@@ -30784,10 +32657,10 @@
       <c r="D246" t="s">
         <v>9</v>
       </c>
-      <c r="E246" s="24" t="s">
+      <c r="E246" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F246" s="24" t="s">
+      <c r="F246" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G246" t="s">
@@ -30802,7 +32675,7 @@
       <c r="A247" t="s">
         <v>57</v>
       </c>
-      <c r="B247" s="33">
+      <c r="B247" s="23">
         <v>46182</v>
       </c>
       <c r="C247" t="s">
@@ -30811,10 +32684,10 @@
       <c r="D247" t="s">
         <v>9</v>
       </c>
-      <c r="E247" s="24" t="s">
+      <c r="E247" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F247" s="24" t="s">
+      <c r="F247" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G247" t="s">
@@ -30829,7 +32702,7 @@
       <c r="A248" t="s">
         <v>119</v>
       </c>
-      <c r="B248" s="33">
+      <c r="B248" s="23">
         <v>46232</v>
       </c>
       <c r="C248" t="s">
@@ -30838,10 +32711,10 @@
       <c r="D248" t="s">
         <v>9</v>
       </c>
-      <c r="E248" s="24" t="s">
+      <c r="E248" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F248" s="24" t="s">
+      <c r="F248" s="16" t="s">
         <v>88</v>
       </c>
       <c r="G248" t="s">
@@ -30856,7 +32729,7 @@
       <c r="A249" t="s">
         <v>84</v>
       </c>
-      <c r="B249" s="33">
+      <c r="B249" s="23">
         <v>45732</v>
       </c>
       <c r="C249" t="s">
@@ -30865,10 +32738,10 @@
       <c r="D249" t="s">
         <v>9</v>
       </c>
-      <c r="E249" s="24" t="s">
+      <c r="E249" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="F249" s="24" t="s">
+      <c r="F249" s="16" t="s">
         <v>55</v>
       </c>
       <c r="G249" t="s">
@@ -30883,7 +32756,7 @@
       <c r="A250" t="s">
         <v>49</v>
       </c>
-      <c r="B250" s="33">
+      <c r="B250" s="23">
         <v>45776</v>
       </c>
       <c r="C250" t="s">
@@ -30892,10 +32765,10 @@
       <c r="D250" t="s">
         <v>9</v>
       </c>
-      <c r="E250" s="24" t="s">
+      <c r="E250" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F250" s="24" t="s">
+      <c r="F250" s="16" t="s">
         <v>108</v>
       </c>
       <c r="G250" t="s">
@@ -30910,7 +32783,7 @@
       <c r="A251" t="s">
         <v>73</v>
       </c>
-      <c r="B251" s="33">
+      <c r="B251" s="23">
         <v>45764</v>
       </c>
       <c r="C251" t="s">
@@ -30919,10 +32792,10 @@
       <c r="D251" t="s">
         <v>9</v>
       </c>
-      <c r="E251" s="24" t="s">
+      <c r="E251" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F251" s="24" t="s">
+      <c r="F251" s="16" t="s">
         <v>146</v>
       </c>
       <c r="G251" t="s">
@@ -30937,7 +32810,7 @@
       <c r="A252" t="s">
         <v>51</v>
       </c>
-      <c r="B252" s="33">
+      <c r="B252" s="23">
         <v>45873</v>
       </c>
       <c r="C252" t="s">
@@ -30946,10 +32819,10 @@
       <c r="D252" t="s">
         <v>9</v>
       </c>
-      <c r="E252" s="24" t="s">
+      <c r="E252" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F252" s="24" t="s">
+      <c r="F252" s="16" t="s">
         <v>116</v>
       </c>
       <c r="G252" t="s">
@@ -30964,7 +32837,7 @@
       <c r="A253" t="s">
         <v>71</v>
       </c>
-      <c r="B253" s="33">
+      <c r="B253" s="23">
         <v>46069</v>
       </c>
       <c r="C253" t="s">
@@ -30973,10 +32846,10 @@
       <c r="D253" t="s">
         <v>9</v>
       </c>
-      <c r="E253" s="24" t="s">
+      <c r="E253" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F253" s="24" t="s">
+      <c r="F253" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G253" t="s">
@@ -30991,7 +32864,7 @@
       <c r="A254" t="s">
         <v>167</v>
       </c>
-      <c r="B254" s="33">
+      <c r="B254" s="23">
         <v>46020</v>
       </c>
       <c r="C254" t="s">
@@ -31000,10 +32873,10 @@
       <c r="D254" t="s">
         <v>18</v>
       </c>
-      <c r="E254" s="24" t="s">
+      <c r="E254" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F254" s="24" t="s">
+      <c r="F254" s="16" t="s">
         <v>32</v>
       </c>
       <c r="G254" t="s">
@@ -31018,7 +32891,7 @@
       <c r="A255" t="s">
         <v>223</v>
       </c>
-      <c r="B255" s="33">
+      <c r="B255" s="23">
         <v>45831</v>
       </c>
       <c r="C255" t="s">
@@ -31027,10 +32900,10 @@
       <c r="D255" t="s">
         <v>18</v>
       </c>
-      <c r="E255" s="24" t="s">
+      <c r="E255" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F255" s="24" t="s">
+      <c r="F255" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G255" t="s">
@@ -31045,7 +32918,7 @@
       <c r="A256" t="s">
         <v>70</v>
       </c>
-      <c r="B256" s="33">
+      <c r="B256" s="23">
         <v>45858</v>
       </c>
       <c r="C256" t="s">
@@ -31054,10 +32927,10 @@
       <c r="D256" t="s">
         <v>9</v>
       </c>
-      <c r="E256" s="24" t="s">
+      <c r="E256" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F256" s="24" t="s">
+      <c r="F256" s="16" t="s">
         <v>24</v>
       </c>
       <c r="G256" t="s">
@@ -31072,7 +32945,7 @@
       <c r="A257" t="s">
         <v>205</v>
       </c>
-      <c r="B257" s="33">
+      <c r="B257" s="23">
         <v>45872</v>
       </c>
       <c r="C257" t="s">
@@ -31081,10 +32954,10 @@
       <c r="D257" t="s">
         <v>9</v>
       </c>
-      <c r="E257" s="24" t="s">
+      <c r="E257" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F257" s="24">
+      <c r="F257" s="16">
         <v>0.71319444444444446</v>
       </c>
       <c r="G257" t="s">
@@ -31099,7 +32972,7 @@
       <c r="A258" t="s">
         <v>156</v>
       </c>
-      <c r="B258" s="33">
+      <c r="B258" s="23">
         <v>45773</v>
       </c>
       <c r="C258" t="s">
@@ -31108,10 +32981,10 @@
       <c r="D258" t="s">
         <v>9</v>
       </c>
-      <c r="E258" s="24" t="s">
+      <c r="E258" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F258" s="24" t="s">
+      <c r="F258" s="16" t="s">
         <v>94</v>
       </c>
       <c r="G258" t="s">
@@ -31126,7 +32999,7 @@
       <c r="A259" t="s">
         <v>56</v>
       </c>
-      <c r="B259" s="33">
+      <c r="B259" s="23">
         <v>46058</v>
       </c>
       <c r="C259" t="s">
@@ -31135,10 +33008,10 @@
       <c r="D259" t="s">
         <v>9</v>
       </c>
-      <c r="E259" s="24" t="s">
+      <c r="E259" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F259" s="24" t="s">
+      <c r="F259" s="16" t="s">
         <v>146</v>
       </c>
       <c r="G259" t="s">
@@ -31153,7 +33026,7 @@
       <c r="A260" t="s">
         <v>129</v>
       </c>
-      <c r="B260" s="33">
+      <c r="B260" s="23">
         <v>46063</v>
       </c>
       <c r="C260" t="s">
@@ -31162,7 +33035,7 @@
       <c r="D260" t="s">
         <v>9</v>
       </c>
-      <c r="E260" s="24" t="s">
+      <c r="E260" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G260" t="s">
@@ -31177,7 +33050,7 @@
       <c r="A261" t="s">
         <v>89</v>
       </c>
-      <c r="B261" s="33">
+      <c r="B261" s="23">
         <v>46047</v>
       </c>
       <c r="C261" t="s">
@@ -31186,10 +33059,10 @@
       <c r="D261" t="s">
         <v>9</v>
       </c>
-      <c r="E261" s="24" t="s">
+      <c r="E261" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F261" s="24" t="s">
+      <c r="F261" s="16" t="s">
         <v>120</v>
       </c>
       <c r="G261" t="s">
@@ -31204,7 +33077,7 @@
       <c r="A262" t="s">
         <v>34</v>
       </c>
-      <c r="B262" s="33">
+      <c r="B262" s="23">
         <v>45854</v>
       </c>
       <c r="C262" t="s">
@@ -31213,10 +33086,10 @@
       <c r="D262" t="s">
         <v>9</v>
       </c>
-      <c r="E262" s="24" t="s">
+      <c r="E262" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F262" s="24" t="s">
+      <c r="F262" s="16" t="s">
         <v>136</v>
       </c>
       <c r="G262" t="s">
@@ -31242,18 +33115,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C59529B-20BE-4893-AB73-B81BAF0207C8}">
-  <dimension ref="A3:C59"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A3:F65"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="7" t="s">
         <v>259</v>
       </c>
@@ -31261,7 +33134,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:6">
       <c r="A4" s="7" t="s">
         <v>256</v>
       </c>
@@ -31269,40 +33142,156 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6">
       <c r="A5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="33">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33">
+        <v>6</v>
+      </c>
+      <c r="D5" s="33">
+        <v>16</v>
+      </c>
+      <c r="E5" s="33">
+        <v>6</v>
+      </c>
+      <c r="F5" s="33">
         <v>30</v>
       </c>
-      <c r="B5" s="23">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="33">
+        <v>3</v>
+      </c>
+      <c r="C6" s="33">
+        <v>9</v>
+      </c>
+      <c r="D6" s="33">
+        <v>30</v>
+      </c>
+      <c r="E6" s="33">
+        <v>3</v>
+      </c>
+      <c r="F6" s="33">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="33">
         <v>1</v>
       </c>
-      <c r="C5" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8" t="s">
+      <c r="C7" s="33">
+        <v>2</v>
+      </c>
+      <c r="D7" s="33">
+        <v>15</v>
+      </c>
+      <c r="E7" s="33">
+        <v>2</v>
+      </c>
+      <c r="F7" s="33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B8" s="33">
+        <v>7</v>
+      </c>
+      <c r="C8" s="33">
+        <v>13</v>
+      </c>
+      <c r="D8" s="33">
+        <v>49</v>
+      </c>
+      <c r="E8" s="33">
+        <v>7</v>
+      </c>
+      <c r="F8" s="33">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="33">
         <v>2</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C9" s="33">
+        <v>6</v>
+      </c>
+      <c r="D9" s="33">
+        <v>36</v>
+      </c>
+      <c r="E9" s="33">
+        <v>7</v>
+      </c>
+      <c r="F9" s="33">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="33">
+        <v>6</v>
+      </c>
+      <c r="C10" s="33">
+        <v>9</v>
+      </c>
+      <c r="D10" s="33">
+        <v>22</v>
+      </c>
+      <c r="E10" s="33">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="8" t="s">
+      <c r="F10" s="33">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="23">
-        <v>3</v>
-      </c>
-      <c r="C7" s="23">
-        <v>3</v>
+      <c r="B11" s="33">
+        <v>21</v>
+      </c>
+      <c r="C11" s="33">
+        <v>45</v>
+      </c>
+      <c r="D11" s="33">
+        <v>168</v>
+      </c>
+      <c r="E11" s="33">
+        <v>27</v>
+      </c>
+      <c r="F11" s="33">
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -31315,115 +33304,194 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="33">
         <v>30</v>
-      </c>
-      <c r="B20" s="23">
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="23">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="B21" s="33">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="33">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="33">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="33">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B22" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="7" t="s">
+      <c r="B26" s="33">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B39" s="7" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="7" t="s">
+    <row r="40" spans="1:6">
+      <c r="A40" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B40" t="s">
         <v>41</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="8" t="s">
+    <row r="41" spans="1:6">
+      <c r="A41" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="23">
-        <v>3</v>
-      </c>
-      <c r="C37" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="8" t="s">
+      <c r="B41" s="33">
+        <v>6</v>
+      </c>
+      <c r="C41" s="33">
+        <v>16</v>
+      </c>
+      <c r="D41" s="33">
+        <v>58</v>
+      </c>
+      <c r="E41" s="33">
+        <v>8</v>
+      </c>
+      <c r="F41" s="33">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="33">
+        <v>15</v>
+      </c>
+      <c r="C42" s="33">
+        <v>29</v>
+      </c>
+      <c r="D42" s="33">
+        <v>110</v>
+      </c>
+      <c r="E42" s="33">
+        <v>19</v>
+      </c>
+      <c r="F42" s="33">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B38" s="23">
-        <v>3</v>
-      </c>
-      <c r="C38" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="7" t="s">
+      <c r="B43" s="33">
+        <v>21</v>
+      </c>
+      <c r="C43" s="33">
+        <v>45</v>
+      </c>
+      <c r="D43" s="33">
+        <v>168</v>
+      </c>
+      <c r="E43" s="33">
+        <v>27</v>
+      </c>
+      <c r="F43" s="33">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B60" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="8" t="s">
+    <row r="61" spans="1:2">
+      <c r="A61" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="23">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="8" t="s">
+      <c r="B61" s="33">
         <v>21</v>
       </c>
-      <c r="B56" s="23">
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62" s="33">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="33">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B57" s="23">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="23">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="8" t="s">
+      <c r="B64" s="33">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B59" s="23">
-        <v>180</v>
+      <c r="B65" s="33">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -31435,13 +33503,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A916E9E-6060-45D0-8717-2939D6A2EDA9}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7265625" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -31465,7 +33533,7 @@
       <c r="R1" s="13"/>
       <c r="Y1" s="11"/>
     </row>
-    <row r="2" spans="1:25" ht="31">
+    <row r="2" spans="1:25" ht="31.5">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
@@ -31491,10 +33559,10 @@
     <row r="3" spans="1:25">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
@@ -31530,72 +33598,72 @@
       <c r="R4" s="13"/>
       <c r="Y4" s="11"/>
     </row>
-    <row r="6" spans="1:25" ht="18.5">
+    <row r="6" spans="1:25" ht="18.75">
       <c r="B6" s="10"/>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="14"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="29"/>
-      <c r="K6" s="31" t="s">
+      <c r="G6" s="20"/>
+      <c r="H6" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="21"/>
+      <c r="K6" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="31"/>
-      <c r="N6" s="16" t="s">
+      <c r="L6" s="32"/>
+      <c r="N6" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="O6" s="16"/>
-      <c r="Q6" s="18" t="s">
+      <c r="O6" s="28"/>
+      <c r="Q6" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="R6" s="18"/>
+      <c r="R6" s="30"/>
     </row>
     <row r="7" spans="1:25" ht="28.5">
       <c r="B7" s="9"/>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <f>COUNTA('cleaned-data'!A2:A262)</f>
         <v>261</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="15"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="30">
+      <c r="G7" s="20"/>
+      <c r="H7" s="22">
         <f>COUNTIF('cleaned-data'!G2:G262,"Present")</f>
         <v>168</v>
       </c>
-      <c r="I7" s="30"/>
-      <c r="K7" s="32">
+      <c r="I7" s="22"/>
+      <c r="K7" s="27">
         <f>COUNTIF('cleaned-data'!G2:G262,"Late")</f>
         <v>45</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="N7" s="17">
+      <c r="L7" s="27"/>
+      <c r="N7" s="29">
         <f>COUNTIF('cleaned-data'!G2:G262,"Absent")</f>
         <v>21</v>
       </c>
-      <c r="O7" s="17"/>
-      <c r="Q7" s="19">
+      <c r="O7" s="29"/>
+      <c r="Q7" s="31">
         <f>COUNTIF('cleaned-data'!G2:G262,"Remote")</f>
         <v>27</v>
       </c>
-      <c r="R7" s="19"/>
+      <c r="R7" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="K6:L6"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="N7:O7"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="K6:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -31617,86 +33685,86 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC0D7E6-F880-46FE-81A9-BDE6DFE5A426}">
   <dimension ref="A2:A19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:1" ht="17.5">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:1" ht="18">
+      <c r="A2" s="17" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="26"/>
+      <c r="A3" s="18"/>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="18" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="19" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="19" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="19" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="18" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="19" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="19" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="18" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="18" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="17.5">
-      <c r="A14" s="25" t="s">
+    <row r="14" spans="1:1" ht="18">
+      <c r="A14" s="17" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="26"/>
+      <c r="A15" s="18"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="19" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="19" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="19" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="19" t="s">
         <v>276</v>
       </c>
     </row>

--- a/excel_project/Employee Attendance Data Analysis.xlsx
+++ b/excel_project/Employee Attendance Data Analysis.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{F94A2101-F726-4F57-986D-72AD153440DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{9D7EAFDF-D859-4F86-87FA-928A73C89F4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9D7EAFDF-D859-4F86-87FA-928A73C89F4C}"/>
   </bookViews>
   <sheets>
     <sheet name="row-data" sheetId="1" r:id="rId1"/>
@@ -17405,7 +17405,7 @@
   <dataFields count="1">
     <dataField name="Count of Employee_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="20">
+  <chartFormats count="10">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -17520,120 +17520,6 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="18" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="13">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -17648,7 +17534,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04E98BA2-B21B-41A9-8D6B-B61CD1B21809}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04E98BA2-B21B-41A9-8D6B-B61CD1B21809}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
   <location ref="A39:F43" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
